--- a/logs/feature_importance_analysis/sway/sway_velocity_feature_importance_analysis.xlsx
+++ b/logs/feature_importance_analysis/sway/sway_velocity_feature_importance_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/feature_importance_analysis/sway/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_0E8152A6D3705E6713582711595ED87656C86716" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE066AE-B9CB-4D51-971E-2F992EE9731D}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_0E8152A6D3705E6713582711595ED87656C86716" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4633407-E40C-4BA9-A131-DB6F8C18EAAE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,13 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="10" r:id="rId3"/>
+    <pivotCache cacheId="7" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="268">
   <si>
     <t>date</t>
   </si>
@@ -636,6 +636,198 @@
   </si>
   <si>
     <t>Promedio de global closed R2</t>
+  </si>
+  <si>
+    <t>15/04/2026 17:09:05</t>
+  </si>
+  <si>
+    <t>04-15_17-09-05_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>['wv', 'rarad', 'ya']</t>
+  </si>
+  <si>
+    <t>[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+  </si>
+  <si>
+    <t>[0, 1, 2]</t>
+  </si>
+  <si>
+    <t>15/04/2026 17:31:17</t>
+  </si>
+  <si>
+    <t>04-15_17-31-17_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 17:31:24</t>
+  </si>
+  <si>
+    <t>04-15_17-31-24_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 17:45:43</t>
+  </si>
+  <si>
+    <t>04-15_17-45-43_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>04-15_17-45-43_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 17:50:22</t>
+  </si>
+  <si>
+    <t>04-15_17-50-22_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 18:12:28</t>
+  </si>
+  <si>
+    <t>04-15_18-12-28_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 18:12:59</t>
+  </si>
+  <si>
+    <t>04-15_18-12-59_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 18:30:11</t>
+  </si>
+  <si>
+    <t>04-15_18-30-11_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 18:30:12</t>
+  </si>
+  <si>
+    <t>04-15_18-30-12_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 18:31:36</t>
+  </si>
+  <si>
+    <t>04-15_18-31-36_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+  </si>
+  <si>
+    <t>15/04/2026 18:53:26</t>
+  </si>
+  <si>
+    <t>04-15_18-53-26_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 18:53:58</t>
+  </si>
+  <si>
+    <t>04-15_18-53-58_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 19:14:30</t>
+  </si>
+  <si>
+    <t>04-15_19-14-30_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 19:14:31</t>
+  </si>
+  <si>
+    <t>04-15_19-14-31_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 19:33:09</t>
+  </si>
+  <si>
+    <t>04-15_19-33-09_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 19:54:58</t>
+  </si>
+  <si>
+    <t>04-15_19-54-58_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 19:55:48</t>
+  </si>
+  <si>
+    <t>04-15_19-55-48_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 20:20:44</t>
+  </si>
+  <si>
+    <t>04-15_20-20-44_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 20:20:50</t>
+  </si>
+  <si>
+    <t>04-15_20-20-50_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 20:34:59</t>
+  </si>
+  <si>
+    <t>04-15_20-34-59_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+  </si>
+  <si>
+    <t>15/04/2026 20:56:35</t>
+  </si>
+  <si>
+    <t>04-15_20-56-35_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 20:57:21</t>
+  </si>
+  <si>
+    <t>04-15_20-57-21_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 21:27:07</t>
+  </si>
+  <si>
+    <t>04-15_21-27-07_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 21:27:14</t>
+  </si>
+  <si>
+    <t>04-15_21-27-14_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 21:56:38</t>
+  </si>
+  <si>
+    <t>04-15_21-56-38_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 22:18:20</t>
+  </si>
+  <si>
+    <t>04-15_22-18-20_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 22:18:57</t>
+  </si>
+  <si>
+    <t>04-15_22-18-57_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 22:55:15</t>
+  </si>
+  <si>
+    <t>04-15_22-55-15_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 22:55:28</t>
+  </si>
+  <si>
+    <t>04-15_22-55-28_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
   </si>
 </sst>
 </file>
@@ -706,6 +898,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -734,20 +940,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -762,7 +954,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46126.414150115743" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="50" xr:uid="{7B345D08-2850-4B4C-A901-4648970A7AC4}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46128.429778124999" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="80" xr:uid="{7B345D08-2850-4B4C-A901-4648970A7AC4}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
@@ -800,12 +992,13 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4.5" maxValue="4.5"/>
     </cacheField>
     <cacheField name="features" numFmtId="0">
-      <sharedItems count="5">
+      <sharedItems count="6">
         <s v="['wv']"/>
         <s v="['wv', 'rarad']"/>
         <s v="['wv', 'sv']"/>
         <s v="['wv', 'yr']"/>
         <s v="['wv', 'ya']"/>
+        <s v="['wv', 'rarad', 'ya']"/>
       </sharedItems>
     </cacheField>
     <cacheField name="targets" numFmtId="0">
@@ -848,7 +1041,11 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="reps" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5" count="3">
+        <n v="1"/>
+        <n v="3"/>
+        <n v="5"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="map" numFmtId="0">
       <sharedItems/>
@@ -881,25 +1078,25 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="total params" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="40" maxValue="40"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="40" maxValue="80"/>
     </cacheField>
     <cacheField name="q params" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="10"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="50"/>
     </cacheField>
     <cacheField name="c params" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="30" maxValue="30"/>
     </cacheField>
     <cacheField name="final val loss" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4.6356191010796501E-2" maxValue="0.23030870209427279"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4.6316939676489199E-2" maxValue="0.23030870209427279"/>
     </cacheField>
     <cacheField name="Val Global Open MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="8.0672464402693992E-3" maxValue="0.1196045680209825"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="7.9968593479565996E-3" maxValue="0.1196045680209825"/>
     </cacheField>
     <cacheField name="Val Global Open R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.60278898814887638" maxValue="0.97320838848872682"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.60278898814887638" maxValue="0.97344214651838623"/>
     </cacheField>
     <cacheField name="Val Global Closed R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-3.3515616015406642" maxValue="0.92341034361456364"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-3.3515616015406642" maxValue="0.92455169374918456"/>
     </cacheField>
     <cacheField name="step MSE" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.0988212243568005E-3" maxValue="0.11258926607271311"/>
@@ -1022,7 +1219,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="80">
   <r>
     <s v="13/04/2026 13:47:23"/>
     <s v="04-13_13-47-23_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
@@ -1045,7 +1242,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, -1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1123,7 +1320,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, -1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1201,7 +1398,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, -1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1279,7 +1476,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, -1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1357,7 +1554,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, -1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1435,7 +1632,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, -1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1513,7 +1710,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, -1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1591,7 +1788,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, -1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1669,7 +1866,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, -1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1747,7 +1944,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, -1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1825,7 +2022,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1903,7 +2100,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1981,7 +2178,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2059,7 +2256,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2137,7 +2334,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2215,7 +2412,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2293,7 +2490,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2371,7 +2568,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2449,7 +2646,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2527,7 +2724,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2605,7 +2802,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2683,7 +2880,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2761,7 +2958,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2839,7 +3036,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2917,7 +3114,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2995,7 +3192,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3073,7 +3270,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3151,7 +3348,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3229,7 +3426,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3307,7 +3504,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3385,7 +3582,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3463,7 +3660,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3541,7 +3738,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3619,7 +3816,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3697,7 +3894,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3775,7 +3972,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3853,7 +4050,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3931,7 +4128,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4009,7 +4206,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4087,7 +4284,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4165,7 +4362,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4243,7 +4440,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4321,7 +4518,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4399,7 +4596,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4477,7 +4674,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4555,7 +4752,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4633,7 +4830,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4711,7 +4908,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4789,7 +4986,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4867,7 +5064,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
+    <x v="0"/>
     <s v="[0, 1, -1]"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4923,12 +5120,2512 @@
     <m/>
     <m/>
   </r>
+  <r>
+    <s v="15/04/2026 17:09:05"/>
+    <s v="04-15_17-09-05_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="0"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="7.8525293947116104E-2"/>
+    <n v="8.6438019028373999E-3"/>
+    <n v="0.971293627351554"/>
+    <n v="0.92455169374918456"/>
+    <n v="9.4243151227610001E-3"/>
+    <n v="0.96734676096380756"/>
+    <n v="9.4243151227610001E-3"/>
+    <n v="9.4243151227610001E-3"/>
+    <n v="0.96734676096380756"/>
+    <n v="2.50415875947608E-2"/>
+    <n v="0.91323624741678644"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="9.4243151227610001E-3"/>
+    <n v="0.96734676096380756"/>
+    <n v="9.4243151227610001E-3"/>
+    <n v="9.4243151227610001E-3"/>
+    <n v="0.96734676096380756"/>
+    <n v="2.50415875947608E-2"/>
+    <n v="0.91323624741678644"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 17:31:17"/>
+    <s v="04-15_17-31-17_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="1"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="0.1062790461278903"/>
+    <n v="7.9968593479565996E-3"/>
+    <n v="0.97344214651838623"/>
+    <n v="0.89221847695838896"/>
+    <n v="9.1423828587686995E-3"/>
+    <n v="0.96832359604288099"/>
+    <n v="9.1423828587686995E-3"/>
+    <n v="9.1423828587686995E-3"/>
+    <n v="0.96832359604288099"/>
+    <n v="4.32806863990359E-2"/>
+    <n v="0.85004166560337158"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="9.1423828587686995E-3"/>
+    <n v="0.96832359604288099"/>
+    <n v="9.1423828587686995E-3"/>
+    <n v="9.1423828587686995E-3"/>
+    <n v="0.96832359604288099"/>
+    <n v="4.32806863990359E-2"/>
+    <n v="0.85004166560337158"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 17:31:24"/>
+    <s v="04-15_17-31-24_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="2"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="5.9373371484529397E-2"/>
+    <n v="8.5133707670420992E-3"/>
+    <n v="0.9717267937789188"/>
+    <n v="0.90799304062871899"/>
+    <n v="9.5598561615319998E-3"/>
+    <n v="0.96687714021359361"/>
+    <n v="9.5598561615319998E-3"/>
+    <n v="9.5598561615319998E-3"/>
+    <n v="0.96687714021359361"/>
+    <n v="2.7777888668656499E-2"/>
+    <n v="0.90375554862042362"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="9.5598561615319998E-3"/>
+    <n v="0.96687714021359361"/>
+    <n v="9.5598561615319998E-3"/>
+    <n v="9.5598561615319998E-3"/>
+    <n v="0.96687714021359361"/>
+    <n v="2.7777888668656499E-2"/>
+    <n v="0.90375554862042362"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 17:45:43"/>
+    <s v="04-15_17-45-43_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="3"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="6.2195497811332497E-2"/>
+    <n v="8.2594124365244995E-3"/>
+    <n v="0.97257019840051484"/>
+    <n v="0.84666034279831881"/>
+    <n v="9.4981842340730992E-3"/>
+    <n v="0.96709082027022464"/>
+    <n v="9.4981842340730992E-3"/>
+    <n v="9.4981842340730992E-3"/>
+    <n v="0.96709082027022464"/>
+    <n v="4.2421623651811499E-2"/>
+    <n v="0.85301813454215503"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="9.4981842340730992E-3"/>
+    <n v="0.96709082027022464"/>
+    <n v="9.4981842340730992E-3"/>
+    <n v="9.4981842340730992E-3"/>
+    <n v="0.96709082027022464"/>
+    <n v="4.2421623651811499E-2"/>
+    <n v="0.85301813454215503"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 17:45:43"/>
+    <s v="04-15_17-45-43_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="4"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="4.6316939676489199E-2"/>
+    <n v="9.4521225036424995E-3"/>
+    <n v="0.96860916597137037"/>
+    <n v="0.87543615214065684"/>
+    <n v="1.0321460947417999E-2"/>
+    <n v="0.96423834229558036"/>
+    <n v="1.0321460947417999E-2"/>
+    <n v="1.0321460947417999E-2"/>
+    <n v="0.96423834229558036"/>
+    <n v="4.9771832940988102E-2"/>
+    <n v="0.82755122922763824"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.0321460947417999E-2"/>
+    <n v="0.96423834229558036"/>
+    <n v="1.0321460947417999E-2"/>
+    <n v="1.0321460947417999E-2"/>
+    <n v="0.96423834229558036"/>
+    <n v="4.9771832940988102E-2"/>
+    <n v="0.82755122922763824"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 17:50:22"/>
+    <s v="04-15_17-50-22_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="5"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="8.3849857538528597E-2"/>
+    <n v="8.1888024507249992E-3"/>
+    <n v="0.97280469666734781"/>
+    <n v="0.89024638459836214"/>
+    <n v="9.1184429807078006E-3"/>
+    <n v="0.9684065426072348"/>
+    <n v="9.1184429807078006E-3"/>
+    <n v="9.1184429807078006E-3"/>
+    <n v="0.9684065426072348"/>
+    <n v="4.61178224718806E-2"/>
+    <n v="0.84021159507219223"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="9.1184429807078006E-3"/>
+    <n v="0.9684065426072348"/>
+    <n v="9.1184429807078006E-3"/>
+    <n v="9.1184429807078006E-3"/>
+    <n v="0.9684065426072348"/>
+    <n v="4.61178224718806E-2"/>
+    <n v="0.84021159507219223"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 18:12:28"/>
+    <s v="04-15_18-12-28_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="6"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="5.20010700276924E-2"/>
+    <n v="9.1816932958993999E-3"/>
+    <n v="0.96950727096032763"/>
+    <n v="0.88015478690441895"/>
+    <n v="9.9864365639722001E-3"/>
+    <n v="0.96539913022903856"/>
+    <n v="9.9864365639722001E-3"/>
+    <n v="9.9864365639722001E-3"/>
+    <n v="0.96539913022903856"/>
+    <n v="3.1557348592220001E-2"/>
+    <n v="0.89066052720992606"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="9.9864365639722001E-3"/>
+    <n v="0.96539913022903856"/>
+    <n v="9.9864365639722001E-3"/>
+    <n v="9.9864365639722001E-3"/>
+    <n v="0.96539913022903856"/>
+    <n v="3.1557348592220001E-2"/>
+    <n v="0.89066052720992606"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 18:12:59"/>
+    <s v="04-15_18-12-59_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="7"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="7.2634612605852994E-2"/>
+    <n v="9.3255454079402E-3"/>
+    <n v="0.96902953299491279"/>
+    <n v="0.91033416483244722"/>
+    <n v="1.0289871914808501E-2"/>
+    <n v="0.96434779154672301"/>
+    <n v="1.0289871914808501E-2"/>
+    <n v="1.0289871914808501E-2"/>
+    <n v="0.96434779154672301"/>
+    <n v="2.9048442332671301E-2"/>
+    <n v="0.89935335154201856"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.0289871914808501E-2"/>
+    <n v="0.96434779154672301"/>
+    <n v="1.0289871914808501E-2"/>
+    <n v="1.0289871914808501E-2"/>
+    <n v="0.96434779154672301"/>
+    <n v="2.9048442332671301E-2"/>
+    <n v="0.89935335154201856"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 18:30:11"/>
+    <s v="04-15_18-30-11_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="8"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="5.3857959983475999E-2"/>
+    <n v="8.6693720420853004E-3"/>
+    <n v="0.97120870801233561"/>
+    <n v="0.76551846848774596"/>
+    <n v="9.8124297629965003E-3"/>
+    <n v="0.96600202662969681"/>
+    <n v="9.8124297629965003E-3"/>
+    <n v="9.8124297629965003E-3"/>
+    <n v="0.96600202662969681"/>
+    <n v="0.1105664157295424"/>
+    <n v="0.61691098449453707"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="9.8124297629965003E-3"/>
+    <n v="0.96600202662969681"/>
+    <n v="9.8124297629965003E-3"/>
+    <n v="9.8124297629965003E-3"/>
+    <n v="0.96600202662969681"/>
+    <n v="0.1105664157295424"/>
+    <n v="0.61691098449453707"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 18:30:12"/>
+    <s v="04-15_18-30-12_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="9"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="6.4015801053702498E-2"/>
+    <n v="8.4510607225181007E-3"/>
+    <n v="0.97193372764644059"/>
+    <n v="0.83965410297311593"/>
+    <n v="9.4677475289670996E-3"/>
+    <n v="0.96719627695268418"/>
+    <n v="9.4677475289670996E-3"/>
+    <n v="9.4677475289670996E-3"/>
+    <n v="0.96719627695268418"/>
+    <n v="5.83398816190751E-2"/>
+    <n v="0.79786477053913218"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="9.4677475289670996E-3"/>
+    <n v="0.96719627695268418"/>
+    <n v="9.4677475289670996E-3"/>
+    <n v="9.4677475289670996E-3"/>
+    <n v="0.96719627695268418"/>
+    <n v="5.83398816190751E-2"/>
+    <n v="0.79786477053913218"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 18:31:36"/>
+    <s v="04-15_18-31-36_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="0"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="8.1018805612689301E-2"/>
+    <n v="1.26106883947115E-2"/>
+    <n v="0.95811945663710918"/>
+    <n v="-0.27404308686788448"/>
+    <n v="1.86410997738083E-2"/>
+    <n v="0.93541257068732797"/>
+    <n v="1.86410997738083E-2"/>
+    <n v="1.86410997738083E-2"/>
+    <n v="0.93541257068732797"/>
+    <n v="0.37444965688912818"/>
+    <n v="-0.2973880854101571"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.86410997738083E-2"/>
+    <n v="0.93541257068732797"/>
+    <n v="1.86410997738083E-2"/>
+    <n v="1.86410997738083E-2"/>
+    <n v="0.93541257068732797"/>
+    <n v="0.37444965688912818"/>
+    <n v="-0.2973880854101571"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 18:53:26"/>
+    <s v="04-15_18-53-26_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="1"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="6.3254635499351397E-2"/>
+    <n v="1.14967809788526E-2"/>
+    <n v="0.9618187826668988"/>
+    <n v="0.49185950270771311"/>
+    <n v="1.58892037281343E-2"/>
+    <n v="0.94494730273009719"/>
+    <n v="1.58892037281343E-2"/>
+    <n v="1.58892037281343E-2"/>
+    <n v="0.94494730273009719"/>
+    <n v="0.23422789240643849"/>
+    <n v="0.18845037967594269"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.58892037281343E-2"/>
+    <n v="0.94494730273009719"/>
+    <n v="1.58892037281343E-2"/>
+    <n v="1.58892037281343E-2"/>
+    <n v="0.94494730273009719"/>
+    <n v="0.23422789240643849"/>
+    <n v="0.18845037967594269"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 18:53:58"/>
+    <s v="04-15_18-53-58_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="2"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="7.9143646248638802E-2"/>
+    <n v="1.48665345260563E-2"/>
+    <n v="0.95062771163741355"/>
+    <n v="-1.121598824631991"/>
+    <n v="2.24105749371213E-2"/>
+    <n v="0.92235214433853319"/>
+    <n v="2.24105749371213E-2"/>
+    <n v="2.24105749371213E-2"/>
+    <n v="0.92235214433853319"/>
+    <n v="0.55884837254281883"/>
+    <n v="-0.93629025090171203"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="2.24105749371213E-2"/>
+    <n v="0.92235214433853319"/>
+    <n v="2.24105749371213E-2"/>
+    <n v="2.24105749371213E-2"/>
+    <n v="0.92235214433853319"/>
+    <n v="0.55884837254281883"/>
+    <n v="-0.93629025090171203"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 19:14:30"/>
+    <s v="04-15_19-14-30_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="3"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="7.6273134943670495E-2"/>
+    <n v="1.3079326918650601E-2"/>
+    <n v="0.95656309148010599"/>
+    <n v="-0.68819207276990513"/>
+    <n v="1.71916940040466E-2"/>
+    <n v="0.94043445211255339"/>
+    <n v="1.71916940040466E-2"/>
+    <n v="1.71916940040466E-2"/>
+    <n v="0.94043445211255339"/>
+    <n v="0.49565441153559509"/>
+    <n v="-0.71733667310494575"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.71916940040466E-2"/>
+    <n v="0.94043445211255339"/>
+    <n v="1.71916940040466E-2"/>
+    <n v="1.71916940040466E-2"/>
+    <n v="0.94043445211255339"/>
+    <n v="0.49565441153559509"/>
+    <n v="-0.71733667310494575"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 19:14:31"/>
+    <s v="04-15_19-14-31_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="4"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="6.7982921670461202E-2"/>
+    <n v="1.19942413132998E-2"/>
+    <n v="0.96016669925511045"/>
+    <n v="-0.98995772169059504"/>
+    <n v="1.4742156024608301E-2"/>
+    <n v="0.94892157803405963"/>
+    <n v="1.4742156024608301E-2"/>
+    <n v="1.4742156024608301E-2"/>
+    <n v="0.94892157803405963"/>
+    <n v="0.54801454152373019"/>
+    <n v="-0.89875334033198384"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.4742156024608301E-2"/>
+    <n v="0.94892157803405963"/>
+    <n v="1.4742156024608301E-2"/>
+    <n v="1.4742156024608301E-2"/>
+    <n v="0.94892157803405963"/>
+    <n v="0.54801454152373019"/>
+    <n v="-0.89875334033198384"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 19:33:09"/>
+    <s v="04-15_19-33-09_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="5"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="7.9171922349785803E-2"/>
+    <n v="1.5968425746968301E-2"/>
+    <n v="0.9469682918171648"/>
+    <n v="-1.346176847559571"/>
+    <n v="2.02119133326614E-2"/>
+    <n v="0.92997003720342042"/>
+    <n v="2.02119133326614E-2"/>
+    <n v="2.02119133326614E-2"/>
+    <n v="0.92997003720342042"/>
+    <n v="0.55292003218326014"/>
+    <n v="-0.91574981774269604"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="2.02119133326614E-2"/>
+    <n v="0.92997003720342042"/>
+    <n v="2.02119133326614E-2"/>
+    <n v="2.02119133326614E-2"/>
+    <n v="0.92997003720342042"/>
+    <n v="0.55292003218326014"/>
+    <n v="-0.91574981774269604"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 19:54:58"/>
+    <s v="04-15_19-54-58_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="6"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="5.26718021793404E-2"/>
+    <n v="1.2704441806197999E-2"/>
+    <n v="0.9578080982328504"/>
+    <n v="-0.28991001690159313"/>
+    <n v="1.6810773811274E-2"/>
+    <n v="0.94175425922280975"/>
+    <n v="1.6810773811274E-2"/>
+    <n v="1.6810773811274E-2"/>
+    <n v="0.94175425922280975"/>
+    <n v="0.3907958805256061"/>
+    <n v="-0.35402425905123969"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.6810773811274E-2"/>
+    <n v="0.94175425922280975"/>
+    <n v="1.6810773811274E-2"/>
+    <n v="1.6810773811274E-2"/>
+    <n v="0.94175425922280975"/>
+    <n v="0.3907958805256061"/>
+    <n v="-0.35402425905123969"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 19:55:48"/>
+    <s v="04-15_19-55-48_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="7"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="7.6908036242940694E-2"/>
+    <n v="1.4146013430681101E-2"/>
+    <n v="0.95302058774649201"/>
+    <n v="-2.537518430430469"/>
+    <n v="1.5273004357762699E-2"/>
+    <n v="0.94708230193933418"/>
+    <n v="1.5273004357762699E-2"/>
+    <n v="1.5273004357762699E-2"/>
+    <n v="0.94708230193933418"/>
+    <n v="0.67652777411966303"/>
+    <n v="-1.3440242431622551"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.5273004357762699E-2"/>
+    <n v="0.94708230193933418"/>
+    <n v="1.5273004357762699E-2"/>
+    <n v="1.5273004357762699E-2"/>
+    <n v="0.94708230193933418"/>
+    <n v="0.67652777411966303"/>
+    <n v="-1.3440242431622551"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 20:20:44"/>
+    <s v="04-15_20-20-44_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="8"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="5.5102986055795999E-2"/>
+    <n v="1.13135146104825E-2"/>
+    <n v="0.96242741677530363"/>
+    <n v="-0.77176179903038578"/>
+    <n v="1.44016605495888E-2"/>
+    <n v="0.95010132213129395"/>
+    <n v="1.44016605495888E-2"/>
+    <n v="1.44016605495888E-2"/>
+    <n v="0.95010132213129395"/>
+    <n v="0.56282271801848371"/>
+    <n v="-0.95006050912619244"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.44016605495888E-2"/>
+    <n v="0.95010132213129395"/>
+    <n v="1.44016605495888E-2"/>
+    <n v="1.44016605495888E-2"/>
+    <n v="0.95010132213129395"/>
+    <n v="0.56282271801848371"/>
+    <n v="-0.95006050912619244"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 20:20:50"/>
+    <s v="04-15_20-20-50_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="9"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="5.48182959182478E-2"/>
+    <n v="1.1199779396441499E-2"/>
+    <n v="0.96280513545444601"/>
+    <n v="0.2144400868082921"/>
+    <n v="1.35655764853707E-2"/>
+    <n v="0.95299817484129401"/>
+    <n v="1.35655764853707E-2"/>
+    <n v="1.35655764853707E-2"/>
+    <n v="0.95299817484129401"/>
+    <n v="0.35354099861383198"/>
+    <n v="-0.22494405019953409"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.35655764853707E-2"/>
+    <n v="0.95299817484129401"/>
+    <n v="1.35655764853707E-2"/>
+    <n v="1.35655764853707E-2"/>
+    <n v="0.95299817484129401"/>
+    <n v="0.35354099861383198"/>
+    <n v="-0.22494405019953409"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 20:34:59"/>
+    <s v="04-15_20-34-59_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="0"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="0.1175497222027318"/>
+    <n v="1.9805189808791399E-2"/>
+    <n v="0.93422626230736017"/>
+    <n v="-0.92647907416048925"/>
+    <n v="2.2142134996563201E-2"/>
+    <n v="0.92328223139862475"/>
+    <n v="2.2142134996563201E-2"/>
+    <n v="2.2142134996563201E-2"/>
+    <n v="0.92328223139862475"/>
+    <n v="0.52645700673408502"/>
+    <n v="-0.82406108658749222"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="2.2142134996563201E-2"/>
+    <n v="0.92328223139862475"/>
+    <n v="2.2142134996563201E-2"/>
+    <n v="2.2142134996563201E-2"/>
+    <n v="0.92328223139862475"/>
+    <n v="0.52645700673408502"/>
+    <n v="-0.82406108658749222"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 20:56:35"/>
+    <s v="04-15_20-56-35_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="1"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="6.3959920420626704E-2"/>
+    <n v="1.60418770966844E-2"/>
+    <n v="0.94672435728000337"/>
+    <n v="7.9023756648857399E-2"/>
+    <n v="2.00969064263532E-2"/>
+    <n v="0.93036851157037204"/>
+    <n v="2.00969064263532E-2"/>
+    <n v="2.00969064263532E-2"/>
+    <n v="0.93036851157037204"/>
+    <n v="0.26951661149108092"/>
+    <n v="6.6182505083238197E-2"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="2.00969064263532E-2"/>
+    <n v="0.93036851157037204"/>
+    <n v="2.00969064263532E-2"/>
+    <n v="2.00969064263532E-2"/>
+    <n v="0.93036851157037204"/>
+    <n v="0.26951661149108092"/>
+    <n v="6.6182505083238197E-2"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 20:57:21"/>
+    <s v="04-15_20-57-21_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="2"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="7.2858124563777105E-2"/>
+    <n v="1.94210431927213E-2"/>
+    <n v="0.93550202684205275"/>
+    <n v="-0.13615874955120219"/>
+    <n v="2.2856676408924099E-2"/>
+    <n v="0.9208064980179862"/>
+    <n v="2.2856676408924099E-2"/>
+    <n v="2.2856676408924099E-2"/>
+    <n v="0.9208064980179862"/>
+    <n v="0.34117426624687452"/>
+    <n v="-0.1820959638595927"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="2.2856676408924099E-2"/>
+    <n v="0.9208064980179862"/>
+    <n v="2.2856676408924099E-2"/>
+    <n v="2.2856676408924099E-2"/>
+    <n v="0.9208064980179862"/>
+    <n v="0.34117426624687452"/>
+    <n v="-0.1820959638595927"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 21:27:07"/>
+    <s v="04-15_21-27-07_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="3"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="7.1830306514445802E-2"/>
+    <n v="1.6258466605144E-2"/>
+    <n v="0.9460050558416464"/>
+    <n v="-0.50160609397747824"/>
+    <n v="1.7667974160849201E-2"/>
+    <n v="0.9387842430941058"/>
+    <n v="1.7667974160849201E-2"/>
+    <n v="1.7667974160849201E-2"/>
+    <n v="0.9387842430941058"/>
+    <n v="0.42842198710792379"/>
+    <n v="-0.48439068209946679"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.7667974160849201E-2"/>
+    <n v="0.9387842430941058"/>
+    <n v="1.7667974160849201E-2"/>
+    <n v="1.7667974160849201E-2"/>
+    <n v="0.9387842430941058"/>
+    <n v="0.42842198710792379"/>
+    <n v="-0.48439068209946679"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 21:27:14"/>
+    <s v="04-15_21-27-14_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="4"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="5.8240539245228699E-2"/>
+    <n v="1.52665596587167E-2"/>
+    <n v="0.94929921398603623"/>
+    <n v="-0.46106698875157609"/>
+    <n v="1.8232040616981901E-2"/>
+    <n v="0.93682987329805401"/>
+    <n v="1.8232040616981901E-2"/>
+    <n v="1.8232040616981901E-2"/>
+    <n v="0.93682987329805401"/>
+    <n v="0.43637245060924618"/>
+    <n v="-0.51193734005556735"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.8232040616981901E-2"/>
+    <n v="0.93682987329805401"/>
+    <n v="1.8232040616981901E-2"/>
+    <n v="1.8232040616981901E-2"/>
+    <n v="0.93682987329805401"/>
+    <n v="0.43637245060924618"/>
+    <n v="-0.51193734005556735"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 21:56:38"/>
+    <s v="04-15_21-56-38_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="5"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="8.0777425155601296E-2"/>
+    <n v="1.9021958250905201E-2"/>
+    <n v="0.936827402086295"/>
+    <n v="-0.50926086149150063"/>
+    <n v="2.3588723244885298E-2"/>
+    <n v="0.91827011208341558"/>
+    <n v="2.3588723244885298E-2"/>
+    <n v="2.3588723244885298E-2"/>
+    <n v="0.91827011208341558"/>
+    <n v="0.47022945696878887"/>
+    <n v="-0.6292446358438839"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="2.3588723244885298E-2"/>
+    <n v="0.91827011208341558"/>
+    <n v="2.3588723244885298E-2"/>
+    <n v="2.3588723244885298E-2"/>
+    <n v="0.91827011208341558"/>
+    <n v="0.47022945696878887"/>
+    <n v="-0.6292446358438839"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 22:18:20"/>
+    <s v="04-15_22-18-20_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="6"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="5.9151062765839001E-2"/>
+    <n v="1.8484608016264299E-2"/>
+    <n v="0.93861196127121438"/>
+    <n v="-3.3766767427696603E-2"/>
+    <n v="2.0393658854090901E-2"/>
+    <n v="0.92934032778924125"/>
+    <n v="2.0393658854090901E-2"/>
+    <n v="2.0393658854090901E-2"/>
+    <n v="0.92934032778924125"/>
+    <n v="0.29705222317799629"/>
+    <n v="-2.9222508300610101E-2"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="2.0393658854090901E-2"/>
+    <n v="0.92934032778924125"/>
+    <n v="2.0393658854090901E-2"/>
+    <n v="2.0393658854090901E-2"/>
+    <n v="0.92934032778924125"/>
+    <n v="0.29705222317799629"/>
+    <n v="-2.9222508300610101E-2"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 22:18:57"/>
+    <s v="04-15_22-18-57_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="7"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="5.4188874681042103E-2"/>
+    <n v="1.35308519441628E-2"/>
+    <n v="0.95506356085826238"/>
+    <n v="0.1885492978150263"/>
+    <n v="1.72155310404415E-2"/>
+    <n v="0.94035186187260722"/>
+    <n v="1.72155310404415E-2"/>
+    <n v="1.72155310404415E-2"/>
+    <n v="0.94035186187260722"/>
+    <n v="0.25060475085835782"/>
+    <n v="0.13170806294240109"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.72155310404415E-2"/>
+    <n v="0.94035186187260722"/>
+    <n v="1.72155310404415E-2"/>
+    <n v="1.72155310404415E-2"/>
+    <n v="0.94035186187260722"/>
+    <n v="0.25060475085835782"/>
+    <n v="0.13170806294240109"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 22:55:15"/>
+    <s v="04-15_22-55-15_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="8"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="6.7964925006429602E-2"/>
+    <n v="1.8756596596358501E-2"/>
+    <n v="0.93770867755137999"/>
+    <n v="-0.23741663021914869"/>
+    <n v="2.4160365616291E-2"/>
+    <n v="0.91628949335902243"/>
+    <n v="2.4160365616291E-2"/>
+    <n v="2.4160365616291E-2"/>
+    <n v="0.91628949335902243"/>
+    <n v="0.35232038875783661"/>
+    <n v="-0.22071489774881781"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="2.4160365616291E-2"/>
+    <n v="0.91628949335902243"/>
+    <n v="2.4160365616291E-2"/>
+    <n v="2.4160365616291E-2"/>
+    <n v="0.91628949335902243"/>
+    <n v="0.35232038875783661"/>
+    <n v="-0.22071489774881781"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 22:55:28"/>
+    <s v="04-15_22-55-28_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="9"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Sway Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <s v="[0, 1, 2]"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="6.56548478243969E-2"/>
+    <n v="1.53856241943085E-2"/>
+    <n v="0.94890379644103318"/>
+    <n v="5.2215333591930299E-2"/>
+    <n v="1.8991631709616999E-2"/>
+    <n v="0.93419805239706644"/>
+    <n v="1.8991631709616999E-2"/>
+    <n v="1.8991631709616999E-2"/>
+    <n v="0.93419805239706644"/>
+    <n v="0.23447876511905949"/>
+    <n v="0.1875811593086093"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.8991631709616999E-2"/>
+    <n v="0.93419805239706644"/>
+    <n v="1.8991631709616999E-2"/>
+    <n v="1.8991631709616999E-2"/>
+    <n v="0.93419805239706644"/>
+    <n v="0.23447876511905949"/>
+    <n v="0.1875811593086093"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{54A40713-372C-4F77-B67C-35CD2F878E3D}" name="TablaDinámica1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A1:D7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74B516EA-FFFB-4317-81BF-860DEAF56415}" name="TablaDinámica2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="F3:H7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="76">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="7">
+        <item sd="0" x="5"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="0"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="21"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="7" item="0" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Promedio de global open R2" fld="43" subtotal="average" baseField="21" baseItem="0"/>
+    <dataField name="Promedio de global closed R2" fld="45" subtotal="average" baseField="21" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{54A40713-372C-4F77-B67C-35CD2F878E3D}" name="TablaDinámica1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:D10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="76">
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -4952,12 +7649,13 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="6">
+      <items count="7">
         <item sd="0" x="1"/>
         <item sd="0" x="2"/>
         <item sd="0" x="4"/>
         <item sd="0" x="3"/>
         <item sd="0" x="0"/>
+        <item sd="0" x="5"/>
         <item t="default" sd="0"/>
       </items>
     </pivotField>
@@ -4974,7 +7672,14 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -5034,7 +7739,7 @@
     <field x="7"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="7">
     <i>
       <x/>
     </i>
@@ -5049,6 +7754,9 @@
     </i>
     <i>
       <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -5068,6 +7776,9 @@
       <x v="2"/>
     </i>
   </colItems>
+  <pageFields count="1">
+    <pageField fld="21" item="0" hier="-1"/>
+  </pageFields>
   <dataFields count="3">
     <dataField name="Promedio de global open R2" fld="43" subtotal="average" baseField="7" baseItem="0"/>
     <dataField name="Promedio de global closed R2" fld="45" subtotal="average" baseField="7" baseItem="0"/>
@@ -5086,8 +7797,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5E22F8A-745D-4DF4-BA3E-BA250AC4E1E1}" name="Tabla1" displayName="Tabla1" ref="A1:BX51" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
-  <autoFilter ref="A1:BX51" xr:uid="{E5E22F8A-745D-4DF4-BA3E-BA250AC4E1E1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5E22F8A-745D-4DF4-BA3E-BA250AC4E1E1}" name="Tabla1" displayName="Tabla1" ref="A1:BX81" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+  <autoFilter ref="A1:BX81" xr:uid="{E5E22F8A-745D-4DF4-BA3E-BA250AC4E1E1}"/>
   <tableColumns count="76">
     <tableColumn id="1" xr3:uid="{E0999DD9-677A-4D67-89F8-F75B68F77AC3}" name="date"/>
     <tableColumn id="2" xr3:uid="{7BCED706-D1A8-44B4-B5D8-D51FCCF20577}" name="model_id"/>
@@ -5455,7 +8166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BX51"/>
+  <dimension ref="A1:BX81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.77734375" customWidth="1"/>
@@ -13954,6 +16665,4926 @@
         <v>-3.137934288132612</v>
       </c>
     </row>
+    <row r="52" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>204</v>
+      </c>
+      <c r="B52" t="s">
+        <v>205</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52" t="s">
+        <v>79</v>
+      </c>
+      <c r="F52">
+        <v>16590</v>
+      </c>
+      <c r="G52">
+        <v>4.5</v>
+      </c>
+      <c r="H52" t="s">
+        <v>206</v>
+      </c>
+      <c r="I52" t="s">
+        <v>81</v>
+      </c>
+      <c r="J52">
+        <v>5</v>
+      </c>
+      <c r="K52">
+        <v>5</v>
+      </c>
+      <c r="L52" t="s">
+        <v>82</v>
+      </c>
+      <c r="M52" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" t="b">
+        <v>0</v>
+      </c>
+      <c r="O52" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>207</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52" t="s">
+        <v>85</v>
+      </c>
+      <c r="T52" t="s">
+        <v>86</v>
+      </c>
+      <c r="U52" t="s">
+        <v>87</v>
+      </c>
+      <c r="V52">
+        <v>1</v>
+      </c>
+      <c r="W52" t="s">
+        <v>208</v>
+      </c>
+      <c r="X52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z52">
+        <v>4000</v>
+      </c>
+      <c r="AA52">
+        <v>4000</v>
+      </c>
+      <c r="AC52">
+        <v>256</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE52">
+        <v>0.15</v>
+      </c>
+      <c r="AF52" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG52">
+        <v>40</v>
+      </c>
+      <c r="AH52">
+        <v>10</v>
+      </c>
+      <c r="AI52">
+        <v>30</v>
+      </c>
+      <c r="AJ52">
+        <v>7.8525293947116104E-2</v>
+      </c>
+      <c r="AK52">
+        <v>8.6438019028373999E-3</v>
+      </c>
+      <c r="AL52">
+        <v>0.971293627351554</v>
+      </c>
+      <c r="AM52">
+        <v>0.92455169374918456</v>
+      </c>
+      <c r="AN52">
+        <v>9.4243151227610001E-3</v>
+      </c>
+      <c r="AO52">
+        <v>0.96734676096380756</v>
+      </c>
+      <c r="AP52">
+        <v>9.4243151227610001E-3</v>
+      </c>
+      <c r="AQ52">
+        <v>9.4243151227610001E-3</v>
+      </c>
+      <c r="AR52">
+        <v>0.96734676096380756</v>
+      </c>
+      <c r="AS52">
+        <v>2.50415875947608E-2</v>
+      </c>
+      <c r="AT52">
+        <v>0.91323624741678644</v>
+      </c>
+      <c r="AU52">
+        <v>0.2</v>
+      </c>
+      <c r="AV52" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD52">
+        <v>9.4243151227610001E-3</v>
+      </c>
+      <c r="BE52">
+        <v>0.96734676096380756</v>
+      </c>
+      <c r="BF52">
+        <v>9.4243151227610001E-3</v>
+      </c>
+      <c r="BG52">
+        <v>9.4243151227610001E-3</v>
+      </c>
+      <c r="BH52">
+        <v>0.96734676096380756</v>
+      </c>
+      <c r="BI52">
+        <v>2.50415875947608E-2</v>
+      </c>
+      <c r="BJ52">
+        <v>0.91323624741678644</v>
+      </c>
+    </row>
+    <row r="53" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>209</v>
+      </c>
+      <c r="B53" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" t="s">
+        <v>78</v>
+      </c>
+      <c r="E53" t="s">
+        <v>79</v>
+      </c>
+      <c r="F53">
+        <v>16590</v>
+      </c>
+      <c r="G53">
+        <v>4.5</v>
+      </c>
+      <c r="H53" t="s">
+        <v>206</v>
+      </c>
+      <c r="I53" t="s">
+        <v>81</v>
+      </c>
+      <c r="J53">
+        <v>5</v>
+      </c>
+      <c r="K53">
+        <v>5</v>
+      </c>
+      <c r="L53" t="s">
+        <v>82</v>
+      </c>
+      <c r="M53" t="b">
+        <v>1</v>
+      </c>
+      <c r="N53" t="b">
+        <v>0</v>
+      </c>
+      <c r="O53" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>207</v>
+      </c>
+      <c r="R53">
+        <v>1</v>
+      </c>
+      <c r="S53" t="s">
+        <v>85</v>
+      </c>
+      <c r="T53" t="s">
+        <v>86</v>
+      </c>
+      <c r="U53" t="s">
+        <v>87</v>
+      </c>
+      <c r="V53">
+        <v>1</v>
+      </c>
+      <c r="W53" t="s">
+        <v>208</v>
+      </c>
+      <c r="X53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z53">
+        <v>4000</v>
+      </c>
+      <c r="AA53">
+        <v>4000</v>
+      </c>
+      <c r="AC53">
+        <v>256</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE53">
+        <v>0.15</v>
+      </c>
+      <c r="AF53" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG53">
+        <v>40</v>
+      </c>
+      <c r="AH53">
+        <v>10</v>
+      </c>
+      <c r="AI53">
+        <v>30</v>
+      </c>
+      <c r="AJ53">
+        <v>0.1062790461278903</v>
+      </c>
+      <c r="AK53">
+        <v>7.9968593479565996E-3</v>
+      </c>
+      <c r="AL53">
+        <v>0.97344214651838623</v>
+      </c>
+      <c r="AM53">
+        <v>0.89221847695838896</v>
+      </c>
+      <c r="AN53">
+        <v>9.1423828587686995E-3</v>
+      </c>
+      <c r="AO53">
+        <v>0.96832359604288099</v>
+      </c>
+      <c r="AP53">
+        <v>9.1423828587686995E-3</v>
+      </c>
+      <c r="AQ53">
+        <v>9.1423828587686995E-3</v>
+      </c>
+      <c r="AR53">
+        <v>0.96832359604288099</v>
+      </c>
+      <c r="AS53">
+        <v>4.32806863990359E-2</v>
+      </c>
+      <c r="AT53">
+        <v>0.85004166560337158</v>
+      </c>
+      <c r="AU53">
+        <v>0.2</v>
+      </c>
+      <c r="AV53" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD53">
+        <v>9.1423828587686995E-3</v>
+      </c>
+      <c r="BE53">
+        <v>0.96832359604288099</v>
+      </c>
+      <c r="BF53">
+        <v>9.1423828587686995E-3</v>
+      </c>
+      <c r="BG53">
+        <v>9.1423828587686995E-3</v>
+      </c>
+      <c r="BH53">
+        <v>0.96832359604288099</v>
+      </c>
+      <c r="BI53">
+        <v>4.32806863990359E-2</v>
+      </c>
+      <c r="BJ53">
+        <v>0.85004166560337158</v>
+      </c>
+    </row>
+    <row r="54" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>211</v>
+      </c>
+      <c r="B54" t="s">
+        <v>212</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54" t="s">
+        <v>97</v>
+      </c>
+      <c r="E54" t="s">
+        <v>79</v>
+      </c>
+      <c r="F54">
+        <v>16590</v>
+      </c>
+      <c r="G54">
+        <v>4.5</v>
+      </c>
+      <c r="H54" t="s">
+        <v>206</v>
+      </c>
+      <c r="I54" t="s">
+        <v>81</v>
+      </c>
+      <c r="J54">
+        <v>5</v>
+      </c>
+      <c r="K54">
+        <v>5</v>
+      </c>
+      <c r="L54" t="s">
+        <v>82</v>
+      </c>
+      <c r="M54" t="b">
+        <v>1</v>
+      </c>
+      <c r="N54" t="b">
+        <v>0</v>
+      </c>
+      <c r="O54" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54">
+        <v>1</v>
+      </c>
+      <c r="S54" t="s">
+        <v>85</v>
+      </c>
+      <c r="T54" t="s">
+        <v>86</v>
+      </c>
+      <c r="U54" t="s">
+        <v>87</v>
+      </c>
+      <c r="V54">
+        <v>1</v>
+      </c>
+      <c r="W54" t="s">
+        <v>208</v>
+      </c>
+      <c r="X54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z54">
+        <v>4000</v>
+      </c>
+      <c r="AA54">
+        <v>4000</v>
+      </c>
+      <c r="AC54">
+        <v>256</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE54">
+        <v>0.15</v>
+      </c>
+      <c r="AF54" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG54">
+        <v>40</v>
+      </c>
+      <c r="AH54">
+        <v>10</v>
+      </c>
+      <c r="AI54">
+        <v>30</v>
+      </c>
+      <c r="AJ54">
+        <v>5.9373371484529397E-2</v>
+      </c>
+      <c r="AK54">
+        <v>8.5133707670420992E-3</v>
+      </c>
+      <c r="AL54">
+        <v>0.9717267937789188</v>
+      </c>
+      <c r="AM54">
+        <v>0.90799304062871899</v>
+      </c>
+      <c r="AN54">
+        <v>9.5598561615319998E-3</v>
+      </c>
+      <c r="AO54">
+        <v>0.96687714021359361</v>
+      </c>
+      <c r="AP54">
+        <v>9.5598561615319998E-3</v>
+      </c>
+      <c r="AQ54">
+        <v>9.5598561615319998E-3</v>
+      </c>
+      <c r="AR54">
+        <v>0.96687714021359361</v>
+      </c>
+      <c r="AS54">
+        <v>2.7777888668656499E-2</v>
+      </c>
+      <c r="AT54">
+        <v>0.90375554862042362</v>
+      </c>
+      <c r="AU54">
+        <v>0.2</v>
+      </c>
+      <c r="AV54" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD54">
+        <v>9.5598561615319998E-3</v>
+      </c>
+      <c r="BE54">
+        <v>0.96687714021359361</v>
+      </c>
+      <c r="BF54">
+        <v>9.5598561615319998E-3</v>
+      </c>
+      <c r="BG54">
+        <v>9.5598561615319998E-3</v>
+      </c>
+      <c r="BH54">
+        <v>0.96687714021359361</v>
+      </c>
+      <c r="BI54">
+        <v>2.7777888668656499E-2</v>
+      </c>
+      <c r="BJ54">
+        <v>0.90375554862042362</v>
+      </c>
+    </row>
+    <row r="55" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>213</v>
+      </c>
+      <c r="B55" t="s">
+        <v>214</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55" t="s">
+        <v>78</v>
+      </c>
+      <c r="E55" t="s">
+        <v>79</v>
+      </c>
+      <c r="F55">
+        <v>16590</v>
+      </c>
+      <c r="G55">
+        <v>4.5</v>
+      </c>
+      <c r="H55" t="s">
+        <v>206</v>
+      </c>
+      <c r="I55" t="s">
+        <v>81</v>
+      </c>
+      <c r="J55">
+        <v>5</v>
+      </c>
+      <c r="K55">
+        <v>5</v>
+      </c>
+      <c r="L55" t="s">
+        <v>82</v>
+      </c>
+      <c r="M55" t="b">
+        <v>1</v>
+      </c>
+      <c r="N55" t="b">
+        <v>0</v>
+      </c>
+      <c r="O55" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>207</v>
+      </c>
+      <c r="R55">
+        <v>1</v>
+      </c>
+      <c r="S55" t="s">
+        <v>85</v>
+      </c>
+      <c r="T55" t="s">
+        <v>86</v>
+      </c>
+      <c r="U55" t="s">
+        <v>87</v>
+      </c>
+      <c r="V55">
+        <v>1</v>
+      </c>
+      <c r="W55" t="s">
+        <v>208</v>
+      </c>
+      <c r="X55" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z55">
+        <v>4000</v>
+      </c>
+      <c r="AA55">
+        <v>4000</v>
+      </c>
+      <c r="AC55">
+        <v>256</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE55">
+        <v>0.15</v>
+      </c>
+      <c r="AF55" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG55">
+        <v>40</v>
+      </c>
+      <c r="AH55">
+        <v>10</v>
+      </c>
+      <c r="AI55">
+        <v>30</v>
+      </c>
+      <c r="AJ55">
+        <v>6.2195497811332497E-2</v>
+      </c>
+      <c r="AK55">
+        <v>8.2594124365244995E-3</v>
+      </c>
+      <c r="AL55">
+        <v>0.97257019840051484</v>
+      </c>
+      <c r="AM55">
+        <v>0.84666034279831881</v>
+      </c>
+      <c r="AN55">
+        <v>9.4981842340730992E-3</v>
+      </c>
+      <c r="AO55">
+        <v>0.96709082027022464</v>
+      </c>
+      <c r="AP55">
+        <v>9.4981842340730992E-3</v>
+      </c>
+      <c r="AQ55">
+        <v>9.4981842340730992E-3</v>
+      </c>
+      <c r="AR55">
+        <v>0.96709082027022464</v>
+      </c>
+      <c r="AS55">
+        <v>4.2421623651811499E-2</v>
+      </c>
+      <c r="AT55">
+        <v>0.85301813454215503</v>
+      </c>
+      <c r="AU55">
+        <v>0.2</v>
+      </c>
+      <c r="AV55" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD55">
+        <v>9.4981842340730992E-3</v>
+      </c>
+      <c r="BE55">
+        <v>0.96709082027022464</v>
+      </c>
+      <c r="BF55">
+        <v>9.4981842340730992E-3</v>
+      </c>
+      <c r="BG55">
+        <v>9.4981842340730992E-3</v>
+      </c>
+      <c r="BH55">
+        <v>0.96709082027022464</v>
+      </c>
+      <c r="BI55">
+        <v>4.2421623651811499E-2</v>
+      </c>
+      <c r="BJ55">
+        <v>0.85301813454215503</v>
+      </c>
+    </row>
+    <row r="56" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>213</v>
+      </c>
+      <c r="B56" t="s">
+        <v>215</v>
+      </c>
+      <c r="C56">
+        <v>4</v>
+      </c>
+      <c r="D56" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56" t="s">
+        <v>79</v>
+      </c>
+      <c r="F56">
+        <v>16590</v>
+      </c>
+      <c r="G56">
+        <v>4.5</v>
+      </c>
+      <c r="H56" t="s">
+        <v>206</v>
+      </c>
+      <c r="I56" t="s">
+        <v>81</v>
+      </c>
+      <c r="J56">
+        <v>5</v>
+      </c>
+      <c r="K56">
+        <v>5</v>
+      </c>
+      <c r="L56" t="s">
+        <v>82</v>
+      </c>
+      <c r="M56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N56" t="b">
+        <v>0</v>
+      </c>
+      <c r="O56" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>207</v>
+      </c>
+      <c r="R56">
+        <v>1</v>
+      </c>
+      <c r="S56" t="s">
+        <v>85</v>
+      </c>
+      <c r="T56" t="s">
+        <v>86</v>
+      </c>
+      <c r="U56" t="s">
+        <v>87</v>
+      </c>
+      <c r="V56">
+        <v>1</v>
+      </c>
+      <c r="W56" t="s">
+        <v>208</v>
+      </c>
+      <c r="X56" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z56">
+        <v>4000</v>
+      </c>
+      <c r="AA56">
+        <v>4000</v>
+      </c>
+      <c r="AC56">
+        <v>256</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE56">
+        <v>0.15</v>
+      </c>
+      <c r="AF56" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG56">
+        <v>40</v>
+      </c>
+      <c r="AH56">
+        <v>10</v>
+      </c>
+      <c r="AI56">
+        <v>30</v>
+      </c>
+      <c r="AJ56">
+        <v>4.6316939676489199E-2</v>
+      </c>
+      <c r="AK56">
+        <v>9.4521225036424995E-3</v>
+      </c>
+      <c r="AL56">
+        <v>0.96860916597137037</v>
+      </c>
+      <c r="AM56">
+        <v>0.87543615214065684</v>
+      </c>
+      <c r="AN56">
+        <v>1.0321460947417999E-2</v>
+      </c>
+      <c r="AO56">
+        <v>0.96423834229558036</v>
+      </c>
+      <c r="AP56">
+        <v>1.0321460947417999E-2</v>
+      </c>
+      <c r="AQ56">
+        <v>1.0321460947417999E-2</v>
+      </c>
+      <c r="AR56">
+        <v>0.96423834229558036</v>
+      </c>
+      <c r="AS56">
+        <v>4.9771832940988102E-2</v>
+      </c>
+      <c r="AT56">
+        <v>0.82755122922763824</v>
+      </c>
+      <c r="AU56">
+        <v>0.2</v>
+      </c>
+      <c r="AV56" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD56">
+        <v>1.0321460947417999E-2</v>
+      </c>
+      <c r="BE56">
+        <v>0.96423834229558036</v>
+      </c>
+      <c r="BF56">
+        <v>1.0321460947417999E-2</v>
+      </c>
+      <c r="BG56">
+        <v>1.0321460947417999E-2</v>
+      </c>
+      <c r="BH56">
+        <v>0.96423834229558036</v>
+      </c>
+      <c r="BI56">
+        <v>4.9771832940988102E-2</v>
+      </c>
+      <c r="BJ56">
+        <v>0.82755122922763824</v>
+      </c>
+    </row>
+    <row r="57" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>216</v>
+      </c>
+      <c r="B57" t="s">
+        <v>217</v>
+      </c>
+      <c r="C57">
+        <v>5</v>
+      </c>
+      <c r="D57" t="s">
+        <v>97</v>
+      </c>
+      <c r="E57" t="s">
+        <v>79</v>
+      </c>
+      <c r="F57">
+        <v>16590</v>
+      </c>
+      <c r="G57">
+        <v>4.5</v>
+      </c>
+      <c r="H57" t="s">
+        <v>206</v>
+      </c>
+      <c r="I57" t="s">
+        <v>81</v>
+      </c>
+      <c r="J57">
+        <v>5</v>
+      </c>
+      <c r="K57">
+        <v>5</v>
+      </c>
+      <c r="L57" t="s">
+        <v>82</v>
+      </c>
+      <c r="M57" t="b">
+        <v>1</v>
+      </c>
+      <c r="N57" t="b">
+        <v>0</v>
+      </c>
+      <c r="O57" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>207</v>
+      </c>
+      <c r="R57">
+        <v>1</v>
+      </c>
+      <c r="S57" t="s">
+        <v>85</v>
+      </c>
+      <c r="T57" t="s">
+        <v>86</v>
+      </c>
+      <c r="U57" t="s">
+        <v>87</v>
+      </c>
+      <c r="V57">
+        <v>1</v>
+      </c>
+      <c r="W57" t="s">
+        <v>208</v>
+      </c>
+      <c r="X57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z57">
+        <v>4000</v>
+      </c>
+      <c r="AA57">
+        <v>4000</v>
+      </c>
+      <c r="AC57">
+        <v>256</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE57">
+        <v>0.15</v>
+      </c>
+      <c r="AF57" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG57">
+        <v>40</v>
+      </c>
+      <c r="AH57">
+        <v>10</v>
+      </c>
+      <c r="AI57">
+        <v>30</v>
+      </c>
+      <c r="AJ57">
+        <v>8.3849857538528597E-2</v>
+      </c>
+      <c r="AK57">
+        <v>8.1888024507249992E-3</v>
+      </c>
+      <c r="AL57">
+        <v>0.97280469666734781</v>
+      </c>
+      <c r="AM57">
+        <v>0.89024638459836214</v>
+      </c>
+      <c r="AN57">
+        <v>9.1184429807078006E-3</v>
+      </c>
+      <c r="AO57">
+        <v>0.9684065426072348</v>
+      </c>
+      <c r="AP57">
+        <v>9.1184429807078006E-3</v>
+      </c>
+      <c r="AQ57">
+        <v>9.1184429807078006E-3</v>
+      </c>
+      <c r="AR57">
+        <v>0.9684065426072348</v>
+      </c>
+      <c r="AS57">
+        <v>4.61178224718806E-2</v>
+      </c>
+      <c r="AT57">
+        <v>0.84021159507219223</v>
+      </c>
+      <c r="AU57">
+        <v>0.2</v>
+      </c>
+      <c r="AV57" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD57">
+        <v>9.1184429807078006E-3</v>
+      </c>
+      <c r="BE57">
+        <v>0.9684065426072348</v>
+      </c>
+      <c r="BF57">
+        <v>9.1184429807078006E-3</v>
+      </c>
+      <c r="BG57">
+        <v>9.1184429807078006E-3</v>
+      </c>
+      <c r="BH57">
+        <v>0.9684065426072348</v>
+      </c>
+      <c r="BI57">
+        <v>4.61178224718806E-2</v>
+      </c>
+      <c r="BJ57">
+        <v>0.84021159507219223</v>
+      </c>
+    </row>
+    <row r="58" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>218</v>
+      </c>
+      <c r="B58" t="s">
+        <v>219</v>
+      </c>
+      <c r="C58">
+        <v>6</v>
+      </c>
+      <c r="D58" t="s">
+        <v>78</v>
+      </c>
+      <c r="E58" t="s">
+        <v>79</v>
+      </c>
+      <c r="F58">
+        <v>16590</v>
+      </c>
+      <c r="G58">
+        <v>4.5</v>
+      </c>
+      <c r="H58" t="s">
+        <v>206</v>
+      </c>
+      <c r="I58" t="s">
+        <v>81</v>
+      </c>
+      <c r="J58">
+        <v>5</v>
+      </c>
+      <c r="K58">
+        <v>5</v>
+      </c>
+      <c r="L58" t="s">
+        <v>82</v>
+      </c>
+      <c r="M58" t="b">
+        <v>1</v>
+      </c>
+      <c r="N58" t="b">
+        <v>0</v>
+      </c>
+      <c r="O58" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>207</v>
+      </c>
+      <c r="R58">
+        <v>1</v>
+      </c>
+      <c r="S58" t="s">
+        <v>85</v>
+      </c>
+      <c r="T58" t="s">
+        <v>86</v>
+      </c>
+      <c r="U58" t="s">
+        <v>87</v>
+      </c>
+      <c r="V58">
+        <v>1</v>
+      </c>
+      <c r="W58" t="s">
+        <v>208</v>
+      </c>
+      <c r="X58" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z58">
+        <v>4000</v>
+      </c>
+      <c r="AA58">
+        <v>4000</v>
+      </c>
+      <c r="AC58">
+        <v>256</v>
+      </c>
+      <c r="AD58" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE58">
+        <v>0.15</v>
+      </c>
+      <c r="AF58" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG58">
+        <v>40</v>
+      </c>
+      <c r="AH58">
+        <v>10</v>
+      </c>
+      <c r="AI58">
+        <v>30</v>
+      </c>
+      <c r="AJ58">
+        <v>5.20010700276924E-2</v>
+      </c>
+      <c r="AK58">
+        <v>9.1816932958993999E-3</v>
+      </c>
+      <c r="AL58">
+        <v>0.96950727096032763</v>
+      </c>
+      <c r="AM58">
+        <v>0.88015478690441895</v>
+      </c>
+      <c r="AN58">
+        <v>9.9864365639722001E-3</v>
+      </c>
+      <c r="AO58">
+        <v>0.96539913022903856</v>
+      </c>
+      <c r="AP58">
+        <v>9.9864365639722001E-3</v>
+      </c>
+      <c r="AQ58">
+        <v>9.9864365639722001E-3</v>
+      </c>
+      <c r="AR58">
+        <v>0.96539913022903856</v>
+      </c>
+      <c r="AS58">
+        <v>3.1557348592220001E-2</v>
+      </c>
+      <c r="AT58">
+        <v>0.89066052720992606</v>
+      </c>
+      <c r="AU58">
+        <v>0.2</v>
+      </c>
+      <c r="AV58" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD58">
+        <v>9.9864365639722001E-3</v>
+      </c>
+      <c r="BE58">
+        <v>0.96539913022903856</v>
+      </c>
+      <c r="BF58">
+        <v>9.9864365639722001E-3</v>
+      </c>
+      <c r="BG58">
+        <v>9.9864365639722001E-3</v>
+      </c>
+      <c r="BH58">
+        <v>0.96539913022903856</v>
+      </c>
+      <c r="BI58">
+        <v>3.1557348592220001E-2</v>
+      </c>
+      <c r="BJ58">
+        <v>0.89066052720992606</v>
+      </c>
+    </row>
+    <row r="59" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>220</v>
+      </c>
+      <c r="B59" t="s">
+        <v>221</v>
+      </c>
+      <c r="C59">
+        <v>7</v>
+      </c>
+      <c r="D59" t="s">
+        <v>97</v>
+      </c>
+      <c r="E59" t="s">
+        <v>79</v>
+      </c>
+      <c r="F59">
+        <v>16590</v>
+      </c>
+      <c r="G59">
+        <v>4.5</v>
+      </c>
+      <c r="H59" t="s">
+        <v>206</v>
+      </c>
+      <c r="I59" t="s">
+        <v>81</v>
+      </c>
+      <c r="J59">
+        <v>5</v>
+      </c>
+      <c r="K59">
+        <v>5</v>
+      </c>
+      <c r="L59" t="s">
+        <v>82</v>
+      </c>
+      <c r="M59" t="b">
+        <v>1</v>
+      </c>
+      <c r="N59" t="b">
+        <v>0</v>
+      </c>
+      <c r="O59" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>207</v>
+      </c>
+      <c r="R59">
+        <v>1</v>
+      </c>
+      <c r="S59" t="s">
+        <v>85</v>
+      </c>
+      <c r="T59" t="s">
+        <v>86</v>
+      </c>
+      <c r="U59" t="s">
+        <v>87</v>
+      </c>
+      <c r="V59">
+        <v>1</v>
+      </c>
+      <c r="W59" t="s">
+        <v>208</v>
+      </c>
+      <c r="X59" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z59">
+        <v>4000</v>
+      </c>
+      <c r="AA59">
+        <v>4000</v>
+      </c>
+      <c r="AC59">
+        <v>256</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE59">
+        <v>0.15</v>
+      </c>
+      <c r="AF59" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG59">
+        <v>40</v>
+      </c>
+      <c r="AH59">
+        <v>10</v>
+      </c>
+      <c r="AI59">
+        <v>30</v>
+      </c>
+      <c r="AJ59">
+        <v>7.2634612605852994E-2</v>
+      </c>
+      <c r="AK59">
+        <v>9.3255454079402E-3</v>
+      </c>
+      <c r="AL59">
+        <v>0.96902953299491279</v>
+      </c>
+      <c r="AM59">
+        <v>0.91033416483244722</v>
+      </c>
+      <c r="AN59">
+        <v>1.0289871914808501E-2</v>
+      </c>
+      <c r="AO59">
+        <v>0.96434779154672301</v>
+      </c>
+      <c r="AP59">
+        <v>1.0289871914808501E-2</v>
+      </c>
+      <c r="AQ59">
+        <v>1.0289871914808501E-2</v>
+      </c>
+      <c r="AR59">
+        <v>0.96434779154672301</v>
+      </c>
+      <c r="AS59">
+        <v>2.9048442332671301E-2</v>
+      </c>
+      <c r="AT59">
+        <v>0.89935335154201856</v>
+      </c>
+      <c r="AU59">
+        <v>0.2</v>
+      </c>
+      <c r="AV59" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD59">
+        <v>1.0289871914808501E-2</v>
+      </c>
+      <c r="BE59">
+        <v>0.96434779154672301</v>
+      </c>
+      <c r="BF59">
+        <v>1.0289871914808501E-2</v>
+      </c>
+      <c r="BG59">
+        <v>1.0289871914808501E-2</v>
+      </c>
+      <c r="BH59">
+        <v>0.96434779154672301</v>
+      </c>
+      <c r="BI59">
+        <v>2.9048442332671301E-2</v>
+      </c>
+      <c r="BJ59">
+        <v>0.89935335154201856</v>
+      </c>
+    </row>
+    <row r="60" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>222</v>
+      </c>
+      <c r="B60" t="s">
+        <v>223</v>
+      </c>
+      <c r="C60">
+        <v>8</v>
+      </c>
+      <c r="D60" t="s">
+        <v>78</v>
+      </c>
+      <c r="E60" t="s">
+        <v>79</v>
+      </c>
+      <c r="F60">
+        <v>16590</v>
+      </c>
+      <c r="G60">
+        <v>4.5</v>
+      </c>
+      <c r="H60" t="s">
+        <v>206</v>
+      </c>
+      <c r="I60" t="s">
+        <v>81</v>
+      </c>
+      <c r="J60">
+        <v>5</v>
+      </c>
+      <c r="K60">
+        <v>5</v>
+      </c>
+      <c r="L60" t="s">
+        <v>82</v>
+      </c>
+      <c r="M60" t="b">
+        <v>1</v>
+      </c>
+      <c r="N60" t="b">
+        <v>0</v>
+      </c>
+      <c r="O60" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>207</v>
+      </c>
+      <c r="R60">
+        <v>1</v>
+      </c>
+      <c r="S60" t="s">
+        <v>85</v>
+      </c>
+      <c r="T60" t="s">
+        <v>86</v>
+      </c>
+      <c r="U60" t="s">
+        <v>87</v>
+      </c>
+      <c r="V60">
+        <v>1</v>
+      </c>
+      <c r="W60" t="s">
+        <v>208</v>
+      </c>
+      <c r="X60" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z60">
+        <v>4000</v>
+      </c>
+      <c r="AA60">
+        <v>4000</v>
+      </c>
+      <c r="AC60">
+        <v>256</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE60">
+        <v>0.15</v>
+      </c>
+      <c r="AF60" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG60">
+        <v>40</v>
+      </c>
+      <c r="AH60">
+        <v>10</v>
+      </c>
+      <c r="AI60">
+        <v>30</v>
+      </c>
+      <c r="AJ60">
+        <v>5.3857959983475999E-2</v>
+      </c>
+      <c r="AK60">
+        <v>8.6693720420853004E-3</v>
+      </c>
+      <c r="AL60">
+        <v>0.97120870801233561</v>
+      </c>
+      <c r="AM60">
+        <v>0.76551846848774596</v>
+      </c>
+      <c r="AN60">
+        <v>9.8124297629965003E-3</v>
+      </c>
+      <c r="AO60">
+        <v>0.96600202662969681</v>
+      </c>
+      <c r="AP60">
+        <v>9.8124297629965003E-3</v>
+      </c>
+      <c r="AQ60">
+        <v>9.8124297629965003E-3</v>
+      </c>
+      <c r="AR60">
+        <v>0.96600202662969681</v>
+      </c>
+      <c r="AS60">
+        <v>0.1105664157295424</v>
+      </c>
+      <c r="AT60">
+        <v>0.61691098449453707</v>
+      </c>
+      <c r="AU60">
+        <v>0.2</v>
+      </c>
+      <c r="AV60" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD60">
+        <v>9.8124297629965003E-3</v>
+      </c>
+      <c r="BE60">
+        <v>0.96600202662969681</v>
+      </c>
+      <c r="BF60">
+        <v>9.8124297629965003E-3</v>
+      </c>
+      <c r="BG60">
+        <v>9.8124297629965003E-3</v>
+      </c>
+      <c r="BH60">
+        <v>0.96600202662969681</v>
+      </c>
+      <c r="BI60">
+        <v>0.1105664157295424</v>
+      </c>
+      <c r="BJ60">
+        <v>0.61691098449453707</v>
+      </c>
+    </row>
+    <row r="61" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>224</v>
+      </c>
+      <c r="B61" t="s">
+        <v>225</v>
+      </c>
+      <c r="C61">
+        <v>9</v>
+      </c>
+      <c r="D61" t="s">
+        <v>78</v>
+      </c>
+      <c r="E61" t="s">
+        <v>79</v>
+      </c>
+      <c r="F61">
+        <v>16590</v>
+      </c>
+      <c r="G61">
+        <v>4.5</v>
+      </c>
+      <c r="H61" t="s">
+        <v>206</v>
+      </c>
+      <c r="I61" t="s">
+        <v>81</v>
+      </c>
+      <c r="J61">
+        <v>5</v>
+      </c>
+      <c r="K61">
+        <v>5</v>
+      </c>
+      <c r="L61" t="s">
+        <v>82</v>
+      </c>
+      <c r="M61" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" t="b">
+        <v>0</v>
+      </c>
+      <c r="O61" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>207</v>
+      </c>
+      <c r="R61">
+        <v>1</v>
+      </c>
+      <c r="S61" t="s">
+        <v>85</v>
+      </c>
+      <c r="T61" t="s">
+        <v>86</v>
+      </c>
+      <c r="U61" t="s">
+        <v>87</v>
+      </c>
+      <c r="V61">
+        <v>1</v>
+      </c>
+      <c r="W61" t="s">
+        <v>208</v>
+      </c>
+      <c r="X61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z61">
+        <v>4000</v>
+      </c>
+      <c r="AA61">
+        <v>4000</v>
+      </c>
+      <c r="AC61">
+        <v>256</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE61">
+        <v>0.15</v>
+      </c>
+      <c r="AF61" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG61">
+        <v>40</v>
+      </c>
+      <c r="AH61">
+        <v>10</v>
+      </c>
+      <c r="AI61">
+        <v>30</v>
+      </c>
+      <c r="AJ61">
+        <v>6.4015801053702498E-2</v>
+      </c>
+      <c r="AK61">
+        <v>8.4510607225181007E-3</v>
+      </c>
+      <c r="AL61">
+        <v>0.97193372764644059</v>
+      </c>
+      <c r="AM61">
+        <v>0.83965410297311593</v>
+      </c>
+      <c r="AN61">
+        <v>9.4677475289670996E-3</v>
+      </c>
+      <c r="AO61">
+        <v>0.96719627695268418</v>
+      </c>
+      <c r="AP61">
+        <v>9.4677475289670996E-3</v>
+      </c>
+      <c r="AQ61">
+        <v>9.4677475289670996E-3</v>
+      </c>
+      <c r="AR61">
+        <v>0.96719627695268418</v>
+      </c>
+      <c r="AS61">
+        <v>5.83398816190751E-2</v>
+      </c>
+      <c r="AT61">
+        <v>0.79786477053913218</v>
+      </c>
+      <c r="AU61">
+        <v>0.2</v>
+      </c>
+      <c r="AV61" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD61">
+        <v>9.4677475289670996E-3</v>
+      </c>
+      <c r="BE61">
+        <v>0.96719627695268418</v>
+      </c>
+      <c r="BF61">
+        <v>9.4677475289670996E-3</v>
+      </c>
+      <c r="BG61">
+        <v>9.4677475289670996E-3</v>
+      </c>
+      <c r="BH61">
+        <v>0.96719627695268418</v>
+      </c>
+      <c r="BI61">
+        <v>5.83398816190751E-2</v>
+      </c>
+      <c r="BJ61">
+        <v>0.79786477053913218</v>
+      </c>
+    </row>
+    <row r="62" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>226</v>
+      </c>
+      <c r="B62" t="s">
+        <v>227</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62" t="s">
+        <v>78</v>
+      </c>
+      <c r="E62" t="s">
+        <v>79</v>
+      </c>
+      <c r="F62">
+        <v>16590</v>
+      </c>
+      <c r="G62">
+        <v>4.5</v>
+      </c>
+      <c r="H62" t="s">
+        <v>206</v>
+      </c>
+      <c r="I62" t="s">
+        <v>81</v>
+      </c>
+      <c r="J62">
+        <v>5</v>
+      </c>
+      <c r="K62">
+        <v>5</v>
+      </c>
+      <c r="L62" t="s">
+        <v>82</v>
+      </c>
+      <c r="M62" t="b">
+        <v>1</v>
+      </c>
+      <c r="N62" t="b">
+        <v>0</v>
+      </c>
+      <c r="O62" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>228</v>
+      </c>
+      <c r="R62">
+        <v>1</v>
+      </c>
+      <c r="S62" t="s">
+        <v>85</v>
+      </c>
+      <c r="T62" t="s">
+        <v>86</v>
+      </c>
+      <c r="U62" t="s">
+        <v>87</v>
+      </c>
+      <c r="V62">
+        <v>3</v>
+      </c>
+      <c r="W62" t="s">
+        <v>208</v>
+      </c>
+      <c r="X62" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z62">
+        <v>4000</v>
+      </c>
+      <c r="AA62">
+        <v>4000</v>
+      </c>
+      <c r="AC62">
+        <v>256</v>
+      </c>
+      <c r="AD62" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE62">
+        <v>0.15</v>
+      </c>
+      <c r="AF62" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG62">
+        <v>60</v>
+      </c>
+      <c r="AH62">
+        <v>30</v>
+      </c>
+      <c r="AI62">
+        <v>30</v>
+      </c>
+      <c r="AJ62">
+        <v>8.1018805612689301E-2</v>
+      </c>
+      <c r="AK62">
+        <v>1.26106883947115E-2</v>
+      </c>
+      <c r="AL62">
+        <v>0.95811945663710918</v>
+      </c>
+      <c r="AM62">
+        <v>-0.27404308686788448</v>
+      </c>
+      <c r="AN62">
+        <v>1.86410997738083E-2</v>
+      </c>
+      <c r="AO62">
+        <v>0.93541257068732797</v>
+      </c>
+      <c r="AP62">
+        <v>1.86410997738083E-2</v>
+      </c>
+      <c r="AQ62">
+        <v>1.86410997738083E-2</v>
+      </c>
+      <c r="AR62">
+        <v>0.93541257068732797</v>
+      </c>
+      <c r="AS62">
+        <v>0.37444965688912818</v>
+      </c>
+      <c r="AT62">
+        <v>-0.2973880854101571</v>
+      </c>
+      <c r="AU62">
+        <v>0.2</v>
+      </c>
+      <c r="AV62" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD62">
+        <v>1.86410997738083E-2</v>
+      </c>
+      <c r="BE62">
+        <v>0.93541257068732797</v>
+      </c>
+      <c r="BF62">
+        <v>1.86410997738083E-2</v>
+      </c>
+      <c r="BG62">
+        <v>1.86410997738083E-2</v>
+      </c>
+      <c r="BH62">
+        <v>0.93541257068732797</v>
+      </c>
+      <c r="BI62">
+        <v>0.37444965688912818</v>
+      </c>
+      <c r="BJ62">
+        <v>-0.2973880854101571</v>
+      </c>
+    </row>
+    <row r="63" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>229</v>
+      </c>
+      <c r="B63" t="s">
+        <v>230</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63" t="s">
+        <v>78</v>
+      </c>
+      <c r="E63" t="s">
+        <v>79</v>
+      </c>
+      <c r="F63">
+        <v>16590</v>
+      </c>
+      <c r="G63">
+        <v>4.5</v>
+      </c>
+      <c r="H63" t="s">
+        <v>206</v>
+      </c>
+      <c r="I63" t="s">
+        <v>81</v>
+      </c>
+      <c r="J63">
+        <v>5</v>
+      </c>
+      <c r="K63">
+        <v>5</v>
+      </c>
+      <c r="L63" t="s">
+        <v>82</v>
+      </c>
+      <c r="M63" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" t="b">
+        <v>0</v>
+      </c>
+      <c r="O63" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>228</v>
+      </c>
+      <c r="R63">
+        <v>1</v>
+      </c>
+      <c r="S63" t="s">
+        <v>85</v>
+      </c>
+      <c r="T63" t="s">
+        <v>86</v>
+      </c>
+      <c r="U63" t="s">
+        <v>87</v>
+      </c>
+      <c r="V63">
+        <v>3</v>
+      </c>
+      <c r="W63" t="s">
+        <v>208</v>
+      </c>
+      <c r="X63" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z63">
+        <v>4000</v>
+      </c>
+      <c r="AA63">
+        <v>4000</v>
+      </c>
+      <c r="AC63">
+        <v>256</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE63">
+        <v>0.15</v>
+      </c>
+      <c r="AF63" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG63">
+        <v>60</v>
+      </c>
+      <c r="AH63">
+        <v>30</v>
+      </c>
+      <c r="AI63">
+        <v>30</v>
+      </c>
+      <c r="AJ63">
+        <v>6.3254635499351397E-2</v>
+      </c>
+      <c r="AK63">
+        <v>1.14967809788526E-2</v>
+      </c>
+      <c r="AL63">
+        <v>0.9618187826668988</v>
+      </c>
+      <c r="AM63">
+        <v>0.49185950270771311</v>
+      </c>
+      <c r="AN63">
+        <v>1.58892037281343E-2</v>
+      </c>
+      <c r="AO63">
+        <v>0.94494730273009719</v>
+      </c>
+      <c r="AP63">
+        <v>1.58892037281343E-2</v>
+      </c>
+      <c r="AQ63">
+        <v>1.58892037281343E-2</v>
+      </c>
+      <c r="AR63">
+        <v>0.94494730273009719</v>
+      </c>
+      <c r="AS63">
+        <v>0.23422789240643849</v>
+      </c>
+      <c r="AT63">
+        <v>0.18845037967594269</v>
+      </c>
+      <c r="AU63">
+        <v>0.2</v>
+      </c>
+      <c r="AV63" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD63">
+        <v>1.58892037281343E-2</v>
+      </c>
+      <c r="BE63">
+        <v>0.94494730273009719</v>
+      </c>
+      <c r="BF63">
+        <v>1.58892037281343E-2</v>
+      </c>
+      <c r="BG63">
+        <v>1.58892037281343E-2</v>
+      </c>
+      <c r="BH63">
+        <v>0.94494730273009719</v>
+      </c>
+      <c r="BI63">
+        <v>0.23422789240643849</v>
+      </c>
+      <c r="BJ63">
+        <v>0.18845037967594269</v>
+      </c>
+    </row>
+    <row r="64" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>231</v>
+      </c>
+      <c r="B64" t="s">
+        <v>232</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64" t="s">
+        <v>78</v>
+      </c>
+      <c r="E64" t="s">
+        <v>79</v>
+      </c>
+      <c r="F64">
+        <v>16590</v>
+      </c>
+      <c r="G64">
+        <v>4.5</v>
+      </c>
+      <c r="H64" t="s">
+        <v>206</v>
+      </c>
+      <c r="I64" t="s">
+        <v>81</v>
+      </c>
+      <c r="J64">
+        <v>5</v>
+      </c>
+      <c r="K64">
+        <v>5</v>
+      </c>
+      <c r="L64" t="s">
+        <v>82</v>
+      </c>
+      <c r="M64" t="b">
+        <v>1</v>
+      </c>
+      <c r="N64" t="b">
+        <v>0</v>
+      </c>
+      <c r="O64" t="b">
+        <v>0</v>
+      </c>
+      <c r="P64" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>228</v>
+      </c>
+      <c r="R64">
+        <v>1</v>
+      </c>
+      <c r="S64" t="s">
+        <v>85</v>
+      </c>
+      <c r="T64" t="s">
+        <v>86</v>
+      </c>
+      <c r="U64" t="s">
+        <v>87</v>
+      </c>
+      <c r="V64">
+        <v>3</v>
+      </c>
+      <c r="W64" t="s">
+        <v>208</v>
+      </c>
+      <c r="X64" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z64">
+        <v>4000</v>
+      </c>
+      <c r="AA64">
+        <v>4000</v>
+      </c>
+      <c r="AC64">
+        <v>256</v>
+      </c>
+      <c r="AD64" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE64">
+        <v>0.15</v>
+      </c>
+      <c r="AF64" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG64">
+        <v>60</v>
+      </c>
+      <c r="AH64">
+        <v>30</v>
+      </c>
+      <c r="AI64">
+        <v>30</v>
+      </c>
+      <c r="AJ64">
+        <v>7.9143646248638802E-2</v>
+      </c>
+      <c r="AK64">
+        <v>1.48665345260563E-2</v>
+      </c>
+      <c r="AL64">
+        <v>0.95062771163741355</v>
+      </c>
+      <c r="AM64">
+        <v>-1.121598824631991</v>
+      </c>
+      <c r="AN64">
+        <v>2.24105749371213E-2</v>
+      </c>
+      <c r="AO64">
+        <v>0.92235214433853319</v>
+      </c>
+      <c r="AP64">
+        <v>2.24105749371213E-2</v>
+      </c>
+      <c r="AQ64">
+        <v>2.24105749371213E-2</v>
+      </c>
+      <c r="AR64">
+        <v>0.92235214433853319</v>
+      </c>
+      <c r="AS64">
+        <v>0.55884837254281883</v>
+      </c>
+      <c r="AT64">
+        <v>-0.93629025090171203</v>
+      </c>
+      <c r="AU64">
+        <v>0.2</v>
+      </c>
+      <c r="AV64" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD64">
+        <v>2.24105749371213E-2</v>
+      </c>
+      <c r="BE64">
+        <v>0.92235214433853319</v>
+      </c>
+      <c r="BF64">
+        <v>2.24105749371213E-2</v>
+      </c>
+      <c r="BG64">
+        <v>2.24105749371213E-2</v>
+      </c>
+      <c r="BH64">
+        <v>0.92235214433853319</v>
+      </c>
+      <c r="BI64">
+        <v>0.55884837254281883</v>
+      </c>
+      <c r="BJ64">
+        <v>-0.93629025090171203</v>
+      </c>
+    </row>
+    <row r="65" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>233</v>
+      </c>
+      <c r="B65" t="s">
+        <v>234</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="D65" t="s">
+        <v>97</v>
+      </c>
+      <c r="E65" t="s">
+        <v>79</v>
+      </c>
+      <c r="F65">
+        <v>16590</v>
+      </c>
+      <c r="G65">
+        <v>4.5</v>
+      </c>
+      <c r="H65" t="s">
+        <v>206</v>
+      </c>
+      <c r="I65" t="s">
+        <v>81</v>
+      </c>
+      <c r="J65">
+        <v>5</v>
+      </c>
+      <c r="K65">
+        <v>5</v>
+      </c>
+      <c r="L65" t="s">
+        <v>82</v>
+      </c>
+      <c r="M65" t="b">
+        <v>1</v>
+      </c>
+      <c r="N65" t="b">
+        <v>0</v>
+      </c>
+      <c r="O65" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>228</v>
+      </c>
+      <c r="R65">
+        <v>1</v>
+      </c>
+      <c r="S65" t="s">
+        <v>85</v>
+      </c>
+      <c r="T65" t="s">
+        <v>86</v>
+      </c>
+      <c r="U65" t="s">
+        <v>87</v>
+      </c>
+      <c r="V65">
+        <v>3</v>
+      </c>
+      <c r="W65" t="s">
+        <v>208</v>
+      </c>
+      <c r="X65" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z65">
+        <v>4000</v>
+      </c>
+      <c r="AA65">
+        <v>4000</v>
+      </c>
+      <c r="AC65">
+        <v>256</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE65">
+        <v>0.15</v>
+      </c>
+      <c r="AF65" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG65">
+        <v>60</v>
+      </c>
+      <c r="AH65">
+        <v>30</v>
+      </c>
+      <c r="AI65">
+        <v>30</v>
+      </c>
+      <c r="AJ65">
+        <v>7.6273134943670495E-2</v>
+      </c>
+      <c r="AK65">
+        <v>1.3079326918650601E-2</v>
+      </c>
+      <c r="AL65">
+        <v>0.95656309148010599</v>
+      </c>
+      <c r="AM65">
+        <v>-0.68819207276990513</v>
+      </c>
+      <c r="AN65">
+        <v>1.71916940040466E-2</v>
+      </c>
+      <c r="AO65">
+        <v>0.94043445211255339</v>
+      </c>
+      <c r="AP65">
+        <v>1.71916940040466E-2</v>
+      </c>
+      <c r="AQ65">
+        <v>1.71916940040466E-2</v>
+      </c>
+      <c r="AR65">
+        <v>0.94043445211255339</v>
+      </c>
+      <c r="AS65">
+        <v>0.49565441153559509</v>
+      </c>
+      <c r="AT65">
+        <v>-0.71733667310494575</v>
+      </c>
+      <c r="AU65">
+        <v>0.2</v>
+      </c>
+      <c r="AV65" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD65">
+        <v>1.71916940040466E-2</v>
+      </c>
+      <c r="BE65">
+        <v>0.94043445211255339</v>
+      </c>
+      <c r="BF65">
+        <v>1.71916940040466E-2</v>
+      </c>
+      <c r="BG65">
+        <v>1.71916940040466E-2</v>
+      </c>
+      <c r="BH65">
+        <v>0.94043445211255339</v>
+      </c>
+      <c r="BI65">
+        <v>0.49565441153559509</v>
+      </c>
+      <c r="BJ65">
+        <v>-0.71733667310494575</v>
+      </c>
+    </row>
+    <row r="66" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>235</v>
+      </c>
+      <c r="B66" t="s">
+        <v>236</v>
+      </c>
+      <c r="C66">
+        <v>4</v>
+      </c>
+      <c r="D66" t="s">
+        <v>97</v>
+      </c>
+      <c r="E66" t="s">
+        <v>79</v>
+      </c>
+      <c r="F66">
+        <v>16590</v>
+      </c>
+      <c r="G66">
+        <v>4.5</v>
+      </c>
+      <c r="H66" t="s">
+        <v>206</v>
+      </c>
+      <c r="I66" t="s">
+        <v>81</v>
+      </c>
+      <c r="J66">
+        <v>5</v>
+      </c>
+      <c r="K66">
+        <v>5</v>
+      </c>
+      <c r="L66" t="s">
+        <v>82</v>
+      </c>
+      <c r="M66" t="b">
+        <v>1</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>228</v>
+      </c>
+      <c r="R66">
+        <v>1</v>
+      </c>
+      <c r="S66" t="s">
+        <v>85</v>
+      </c>
+      <c r="T66" t="s">
+        <v>86</v>
+      </c>
+      <c r="U66" t="s">
+        <v>87</v>
+      </c>
+      <c r="V66">
+        <v>3</v>
+      </c>
+      <c r="W66" t="s">
+        <v>208</v>
+      </c>
+      <c r="X66" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z66">
+        <v>4000</v>
+      </c>
+      <c r="AA66">
+        <v>4000</v>
+      </c>
+      <c r="AC66">
+        <v>256</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE66">
+        <v>0.15</v>
+      </c>
+      <c r="AF66" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG66">
+        <v>60</v>
+      </c>
+      <c r="AH66">
+        <v>30</v>
+      </c>
+      <c r="AI66">
+        <v>30</v>
+      </c>
+      <c r="AJ66">
+        <v>6.7982921670461202E-2</v>
+      </c>
+      <c r="AK66">
+        <v>1.19942413132998E-2</v>
+      </c>
+      <c r="AL66">
+        <v>0.96016669925511045</v>
+      </c>
+      <c r="AM66">
+        <v>-0.98995772169059504</v>
+      </c>
+      <c r="AN66">
+        <v>1.4742156024608301E-2</v>
+      </c>
+      <c r="AO66">
+        <v>0.94892157803405963</v>
+      </c>
+      <c r="AP66">
+        <v>1.4742156024608301E-2</v>
+      </c>
+      <c r="AQ66">
+        <v>1.4742156024608301E-2</v>
+      </c>
+      <c r="AR66">
+        <v>0.94892157803405963</v>
+      </c>
+      <c r="AS66">
+        <v>0.54801454152373019</v>
+      </c>
+      <c r="AT66">
+        <v>-0.89875334033198384</v>
+      </c>
+      <c r="AU66">
+        <v>0.2</v>
+      </c>
+      <c r="AV66" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD66">
+        <v>1.4742156024608301E-2</v>
+      </c>
+      <c r="BE66">
+        <v>0.94892157803405963</v>
+      </c>
+      <c r="BF66">
+        <v>1.4742156024608301E-2</v>
+      </c>
+      <c r="BG66">
+        <v>1.4742156024608301E-2</v>
+      </c>
+      <c r="BH66">
+        <v>0.94892157803405963</v>
+      </c>
+      <c r="BI66">
+        <v>0.54801454152373019</v>
+      </c>
+      <c r="BJ66">
+        <v>-0.89875334033198384</v>
+      </c>
+    </row>
+    <row r="67" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>237</v>
+      </c>
+      <c r="B67" t="s">
+        <v>238</v>
+      </c>
+      <c r="C67">
+        <v>5</v>
+      </c>
+      <c r="D67" t="s">
+        <v>97</v>
+      </c>
+      <c r="E67" t="s">
+        <v>79</v>
+      </c>
+      <c r="F67">
+        <v>16590</v>
+      </c>
+      <c r="G67">
+        <v>4.5</v>
+      </c>
+      <c r="H67" t="s">
+        <v>206</v>
+      </c>
+      <c r="I67" t="s">
+        <v>81</v>
+      </c>
+      <c r="J67">
+        <v>5</v>
+      </c>
+      <c r="K67">
+        <v>5</v>
+      </c>
+      <c r="L67" t="s">
+        <v>82</v>
+      </c>
+      <c r="M67" t="b">
+        <v>1</v>
+      </c>
+      <c r="N67" t="b">
+        <v>0</v>
+      </c>
+      <c r="O67" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>228</v>
+      </c>
+      <c r="R67">
+        <v>1</v>
+      </c>
+      <c r="S67" t="s">
+        <v>85</v>
+      </c>
+      <c r="T67" t="s">
+        <v>86</v>
+      </c>
+      <c r="U67" t="s">
+        <v>87</v>
+      </c>
+      <c r="V67">
+        <v>3</v>
+      </c>
+      <c r="W67" t="s">
+        <v>208</v>
+      </c>
+      <c r="X67" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z67">
+        <v>4000</v>
+      </c>
+      <c r="AA67">
+        <v>4000</v>
+      </c>
+      <c r="AC67">
+        <v>256</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE67">
+        <v>0.15</v>
+      </c>
+      <c r="AF67" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG67">
+        <v>60</v>
+      </c>
+      <c r="AH67">
+        <v>30</v>
+      </c>
+      <c r="AI67">
+        <v>30</v>
+      </c>
+      <c r="AJ67">
+        <v>7.9171922349785803E-2</v>
+      </c>
+      <c r="AK67">
+        <v>1.5968425746968301E-2</v>
+      </c>
+      <c r="AL67">
+        <v>0.9469682918171648</v>
+      </c>
+      <c r="AM67">
+        <v>-1.346176847559571</v>
+      </c>
+      <c r="AN67">
+        <v>2.02119133326614E-2</v>
+      </c>
+      <c r="AO67">
+        <v>0.92997003720342042</v>
+      </c>
+      <c r="AP67">
+        <v>2.02119133326614E-2</v>
+      </c>
+      <c r="AQ67">
+        <v>2.02119133326614E-2</v>
+      </c>
+      <c r="AR67">
+        <v>0.92997003720342042</v>
+      </c>
+      <c r="AS67">
+        <v>0.55292003218326014</v>
+      </c>
+      <c r="AT67">
+        <v>-0.91574981774269604</v>
+      </c>
+      <c r="AU67">
+        <v>0.2</v>
+      </c>
+      <c r="AV67" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD67">
+        <v>2.02119133326614E-2</v>
+      </c>
+      <c r="BE67">
+        <v>0.92997003720342042</v>
+      </c>
+      <c r="BF67">
+        <v>2.02119133326614E-2</v>
+      </c>
+      <c r="BG67">
+        <v>2.02119133326614E-2</v>
+      </c>
+      <c r="BH67">
+        <v>0.92997003720342042</v>
+      </c>
+      <c r="BI67">
+        <v>0.55292003218326014</v>
+      </c>
+      <c r="BJ67">
+        <v>-0.91574981774269604</v>
+      </c>
+    </row>
+    <row r="68" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>239</v>
+      </c>
+      <c r="B68" t="s">
+        <v>240</v>
+      </c>
+      <c r="C68">
+        <v>6</v>
+      </c>
+      <c r="D68" t="s">
+        <v>78</v>
+      </c>
+      <c r="E68" t="s">
+        <v>79</v>
+      </c>
+      <c r="F68">
+        <v>16590</v>
+      </c>
+      <c r="G68">
+        <v>4.5</v>
+      </c>
+      <c r="H68" t="s">
+        <v>206</v>
+      </c>
+      <c r="I68" t="s">
+        <v>81</v>
+      </c>
+      <c r="J68">
+        <v>5</v>
+      </c>
+      <c r="K68">
+        <v>5</v>
+      </c>
+      <c r="L68" t="s">
+        <v>82</v>
+      </c>
+      <c r="M68" t="b">
+        <v>1</v>
+      </c>
+      <c r="N68" t="b">
+        <v>0</v>
+      </c>
+      <c r="O68" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>228</v>
+      </c>
+      <c r="R68">
+        <v>1</v>
+      </c>
+      <c r="S68" t="s">
+        <v>85</v>
+      </c>
+      <c r="T68" t="s">
+        <v>86</v>
+      </c>
+      <c r="U68" t="s">
+        <v>87</v>
+      </c>
+      <c r="V68">
+        <v>3</v>
+      </c>
+      <c r="W68" t="s">
+        <v>208</v>
+      </c>
+      <c r="X68" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z68">
+        <v>4000</v>
+      </c>
+      <c r="AA68">
+        <v>4000</v>
+      </c>
+      <c r="AC68">
+        <v>256</v>
+      </c>
+      <c r="AD68" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE68">
+        <v>0.15</v>
+      </c>
+      <c r="AF68" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG68">
+        <v>60</v>
+      </c>
+      <c r="AH68">
+        <v>30</v>
+      </c>
+      <c r="AI68">
+        <v>30</v>
+      </c>
+      <c r="AJ68">
+        <v>5.26718021793404E-2</v>
+      </c>
+      <c r="AK68">
+        <v>1.2704441806197999E-2</v>
+      </c>
+      <c r="AL68">
+        <v>0.9578080982328504</v>
+      </c>
+      <c r="AM68">
+        <v>-0.28991001690159313</v>
+      </c>
+      <c r="AN68">
+        <v>1.6810773811274E-2</v>
+      </c>
+      <c r="AO68">
+        <v>0.94175425922280975</v>
+      </c>
+      <c r="AP68">
+        <v>1.6810773811274E-2</v>
+      </c>
+      <c r="AQ68">
+        <v>1.6810773811274E-2</v>
+      </c>
+      <c r="AR68">
+        <v>0.94175425922280975</v>
+      </c>
+      <c r="AS68">
+        <v>0.3907958805256061</v>
+      </c>
+      <c r="AT68">
+        <v>-0.35402425905123969</v>
+      </c>
+      <c r="AU68">
+        <v>0.2</v>
+      </c>
+      <c r="AV68" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD68">
+        <v>1.6810773811274E-2</v>
+      </c>
+      <c r="BE68">
+        <v>0.94175425922280975</v>
+      </c>
+      <c r="BF68">
+        <v>1.6810773811274E-2</v>
+      </c>
+      <c r="BG68">
+        <v>1.6810773811274E-2</v>
+      </c>
+      <c r="BH68">
+        <v>0.94175425922280975</v>
+      </c>
+      <c r="BI68">
+        <v>0.3907958805256061</v>
+      </c>
+      <c r="BJ68">
+        <v>-0.35402425905123969</v>
+      </c>
+    </row>
+    <row r="69" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>241</v>
+      </c>
+      <c r="B69" t="s">
+        <v>242</v>
+      </c>
+      <c r="C69">
+        <v>7</v>
+      </c>
+      <c r="D69" t="s">
+        <v>78</v>
+      </c>
+      <c r="E69" t="s">
+        <v>79</v>
+      </c>
+      <c r="F69">
+        <v>16590</v>
+      </c>
+      <c r="G69">
+        <v>4.5</v>
+      </c>
+      <c r="H69" t="s">
+        <v>206</v>
+      </c>
+      <c r="I69" t="s">
+        <v>81</v>
+      </c>
+      <c r="J69">
+        <v>5</v>
+      </c>
+      <c r="K69">
+        <v>5</v>
+      </c>
+      <c r="L69" t="s">
+        <v>82</v>
+      </c>
+      <c r="M69" t="b">
+        <v>1</v>
+      </c>
+      <c r="N69" t="b">
+        <v>0</v>
+      </c>
+      <c r="O69" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>228</v>
+      </c>
+      <c r="R69">
+        <v>1</v>
+      </c>
+      <c r="S69" t="s">
+        <v>85</v>
+      </c>
+      <c r="T69" t="s">
+        <v>86</v>
+      </c>
+      <c r="U69" t="s">
+        <v>87</v>
+      </c>
+      <c r="V69">
+        <v>3</v>
+      </c>
+      <c r="W69" t="s">
+        <v>208</v>
+      </c>
+      <c r="X69" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z69">
+        <v>4000</v>
+      </c>
+      <c r="AA69">
+        <v>4000</v>
+      </c>
+      <c r="AC69">
+        <v>256</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE69">
+        <v>0.15</v>
+      </c>
+      <c r="AF69" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG69">
+        <v>60</v>
+      </c>
+      <c r="AH69">
+        <v>30</v>
+      </c>
+      <c r="AI69">
+        <v>30</v>
+      </c>
+      <c r="AJ69">
+        <v>7.6908036242940694E-2</v>
+      </c>
+      <c r="AK69">
+        <v>1.4146013430681101E-2</v>
+      </c>
+      <c r="AL69">
+        <v>0.95302058774649201</v>
+      </c>
+      <c r="AM69">
+        <v>-2.537518430430469</v>
+      </c>
+      <c r="AN69">
+        <v>1.5273004357762699E-2</v>
+      </c>
+      <c r="AO69">
+        <v>0.94708230193933418</v>
+      </c>
+      <c r="AP69">
+        <v>1.5273004357762699E-2</v>
+      </c>
+      <c r="AQ69">
+        <v>1.5273004357762699E-2</v>
+      </c>
+      <c r="AR69">
+        <v>0.94708230193933418</v>
+      </c>
+      <c r="AS69">
+        <v>0.67652777411966303</v>
+      </c>
+      <c r="AT69">
+        <v>-1.3440242431622551</v>
+      </c>
+      <c r="AU69">
+        <v>0.2</v>
+      </c>
+      <c r="AV69" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD69">
+        <v>1.5273004357762699E-2</v>
+      </c>
+      <c r="BE69">
+        <v>0.94708230193933418</v>
+      </c>
+      <c r="BF69">
+        <v>1.5273004357762699E-2</v>
+      </c>
+      <c r="BG69">
+        <v>1.5273004357762699E-2</v>
+      </c>
+      <c r="BH69">
+        <v>0.94708230193933418</v>
+      </c>
+      <c r="BI69">
+        <v>0.67652777411966303</v>
+      </c>
+      <c r="BJ69">
+        <v>-1.3440242431622551</v>
+      </c>
+    </row>
+    <row r="70" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>243</v>
+      </c>
+      <c r="B70" t="s">
+        <v>244</v>
+      </c>
+      <c r="C70">
+        <v>8</v>
+      </c>
+      <c r="D70" t="s">
+        <v>78</v>
+      </c>
+      <c r="E70" t="s">
+        <v>79</v>
+      </c>
+      <c r="F70">
+        <v>16590</v>
+      </c>
+      <c r="G70">
+        <v>4.5</v>
+      </c>
+      <c r="H70" t="s">
+        <v>206</v>
+      </c>
+      <c r="I70" t="s">
+        <v>81</v>
+      </c>
+      <c r="J70">
+        <v>5</v>
+      </c>
+      <c r="K70">
+        <v>5</v>
+      </c>
+      <c r="L70" t="s">
+        <v>82</v>
+      </c>
+      <c r="M70" t="b">
+        <v>1</v>
+      </c>
+      <c r="N70" t="b">
+        <v>0</v>
+      </c>
+      <c r="O70" t="b">
+        <v>0</v>
+      </c>
+      <c r="P70" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>228</v>
+      </c>
+      <c r="R70">
+        <v>1</v>
+      </c>
+      <c r="S70" t="s">
+        <v>85</v>
+      </c>
+      <c r="T70" t="s">
+        <v>86</v>
+      </c>
+      <c r="U70" t="s">
+        <v>87</v>
+      </c>
+      <c r="V70">
+        <v>3</v>
+      </c>
+      <c r="W70" t="s">
+        <v>208</v>
+      </c>
+      <c r="X70" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z70">
+        <v>4000</v>
+      </c>
+      <c r="AA70">
+        <v>4000</v>
+      </c>
+      <c r="AC70">
+        <v>256</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE70">
+        <v>0.15</v>
+      </c>
+      <c r="AF70" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG70">
+        <v>60</v>
+      </c>
+      <c r="AH70">
+        <v>30</v>
+      </c>
+      <c r="AI70">
+        <v>30</v>
+      </c>
+      <c r="AJ70">
+        <v>5.5102986055795999E-2</v>
+      </c>
+      <c r="AK70">
+        <v>1.13135146104825E-2</v>
+      </c>
+      <c r="AL70">
+        <v>0.96242741677530363</v>
+      </c>
+      <c r="AM70">
+        <v>-0.77176179903038578</v>
+      </c>
+      <c r="AN70">
+        <v>1.44016605495888E-2</v>
+      </c>
+      <c r="AO70">
+        <v>0.95010132213129395</v>
+      </c>
+      <c r="AP70">
+        <v>1.44016605495888E-2</v>
+      </c>
+      <c r="AQ70">
+        <v>1.44016605495888E-2</v>
+      </c>
+      <c r="AR70">
+        <v>0.95010132213129395</v>
+      </c>
+      <c r="AS70">
+        <v>0.56282271801848371</v>
+      </c>
+      <c r="AT70">
+        <v>-0.95006050912619244</v>
+      </c>
+      <c r="AU70">
+        <v>0.2</v>
+      </c>
+      <c r="AV70" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD70">
+        <v>1.44016605495888E-2</v>
+      </c>
+      <c r="BE70">
+        <v>0.95010132213129395</v>
+      </c>
+      <c r="BF70">
+        <v>1.44016605495888E-2</v>
+      </c>
+      <c r="BG70">
+        <v>1.44016605495888E-2</v>
+      </c>
+      <c r="BH70">
+        <v>0.95010132213129395</v>
+      </c>
+      <c r="BI70">
+        <v>0.56282271801848371</v>
+      </c>
+      <c r="BJ70">
+        <v>-0.95006050912619244</v>
+      </c>
+    </row>
+    <row r="71" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>245</v>
+      </c>
+      <c r="B71" t="s">
+        <v>246</v>
+      </c>
+      <c r="C71">
+        <v>9</v>
+      </c>
+      <c r="D71" t="s">
+        <v>78</v>
+      </c>
+      <c r="E71" t="s">
+        <v>79</v>
+      </c>
+      <c r="F71">
+        <v>16590</v>
+      </c>
+      <c r="G71">
+        <v>4.5</v>
+      </c>
+      <c r="H71" t="s">
+        <v>206</v>
+      </c>
+      <c r="I71" t="s">
+        <v>81</v>
+      </c>
+      <c r="J71">
+        <v>5</v>
+      </c>
+      <c r="K71">
+        <v>5</v>
+      </c>
+      <c r="L71" t="s">
+        <v>82</v>
+      </c>
+      <c r="M71" t="b">
+        <v>1</v>
+      </c>
+      <c r="N71" t="b">
+        <v>0</v>
+      </c>
+      <c r="O71" t="b">
+        <v>0</v>
+      </c>
+      <c r="P71" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>228</v>
+      </c>
+      <c r="R71">
+        <v>1</v>
+      </c>
+      <c r="S71" t="s">
+        <v>85</v>
+      </c>
+      <c r="T71" t="s">
+        <v>86</v>
+      </c>
+      <c r="U71" t="s">
+        <v>87</v>
+      </c>
+      <c r="V71">
+        <v>3</v>
+      </c>
+      <c r="W71" t="s">
+        <v>208</v>
+      </c>
+      <c r="X71" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z71">
+        <v>4000</v>
+      </c>
+      <c r="AA71">
+        <v>4000</v>
+      </c>
+      <c r="AC71">
+        <v>256</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE71">
+        <v>0.15</v>
+      </c>
+      <c r="AF71" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG71">
+        <v>60</v>
+      </c>
+      <c r="AH71">
+        <v>30</v>
+      </c>
+      <c r="AI71">
+        <v>30</v>
+      </c>
+      <c r="AJ71">
+        <v>5.48182959182478E-2</v>
+      </c>
+      <c r="AK71">
+        <v>1.1199779396441499E-2</v>
+      </c>
+      <c r="AL71">
+        <v>0.96280513545444601</v>
+      </c>
+      <c r="AM71">
+        <v>0.2144400868082921</v>
+      </c>
+      <c r="AN71">
+        <v>1.35655764853707E-2</v>
+      </c>
+      <c r="AO71">
+        <v>0.95299817484129401</v>
+      </c>
+      <c r="AP71">
+        <v>1.35655764853707E-2</v>
+      </c>
+      <c r="AQ71">
+        <v>1.35655764853707E-2</v>
+      </c>
+      <c r="AR71">
+        <v>0.95299817484129401</v>
+      </c>
+      <c r="AS71">
+        <v>0.35354099861383198</v>
+      </c>
+      <c r="AT71">
+        <v>-0.22494405019953409</v>
+      </c>
+      <c r="AU71">
+        <v>0.2</v>
+      </c>
+      <c r="AV71" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD71">
+        <v>1.35655764853707E-2</v>
+      </c>
+      <c r="BE71">
+        <v>0.95299817484129401</v>
+      </c>
+      <c r="BF71">
+        <v>1.35655764853707E-2</v>
+      </c>
+      <c r="BG71">
+        <v>1.35655764853707E-2</v>
+      </c>
+      <c r="BH71">
+        <v>0.95299817484129401</v>
+      </c>
+      <c r="BI71">
+        <v>0.35354099861383198</v>
+      </c>
+      <c r="BJ71">
+        <v>-0.22494405019953409</v>
+      </c>
+    </row>
+    <row r="72" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>247</v>
+      </c>
+      <c r="B72" t="s">
+        <v>248</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72" t="s">
+        <v>97</v>
+      </c>
+      <c r="E72" t="s">
+        <v>79</v>
+      </c>
+      <c r="F72">
+        <v>16590</v>
+      </c>
+      <c r="G72">
+        <v>4.5</v>
+      </c>
+      <c r="H72" t="s">
+        <v>206</v>
+      </c>
+      <c r="I72" t="s">
+        <v>81</v>
+      </c>
+      <c r="J72">
+        <v>5</v>
+      </c>
+      <c r="K72">
+        <v>5</v>
+      </c>
+      <c r="L72" t="s">
+        <v>82</v>
+      </c>
+      <c r="M72" t="b">
+        <v>1</v>
+      </c>
+      <c r="N72" t="b">
+        <v>0</v>
+      </c>
+      <c r="O72" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>249</v>
+      </c>
+      <c r="R72">
+        <v>1</v>
+      </c>
+      <c r="S72" t="s">
+        <v>85</v>
+      </c>
+      <c r="T72" t="s">
+        <v>86</v>
+      </c>
+      <c r="U72" t="s">
+        <v>87</v>
+      </c>
+      <c r="V72">
+        <v>5</v>
+      </c>
+      <c r="W72" t="s">
+        <v>208</v>
+      </c>
+      <c r="X72" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z72">
+        <v>4000</v>
+      </c>
+      <c r="AA72">
+        <v>4000</v>
+      </c>
+      <c r="AC72">
+        <v>256</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE72">
+        <v>0.15</v>
+      </c>
+      <c r="AF72" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG72">
+        <v>80</v>
+      </c>
+      <c r="AH72">
+        <v>50</v>
+      </c>
+      <c r="AI72">
+        <v>30</v>
+      </c>
+      <c r="AJ72">
+        <v>0.1175497222027318</v>
+      </c>
+      <c r="AK72">
+        <v>1.9805189808791399E-2</v>
+      </c>
+      <c r="AL72">
+        <v>0.93422626230736017</v>
+      </c>
+      <c r="AM72">
+        <v>-0.92647907416048925</v>
+      </c>
+      <c r="AN72">
+        <v>2.2142134996563201E-2</v>
+      </c>
+      <c r="AO72">
+        <v>0.92328223139862475</v>
+      </c>
+      <c r="AP72">
+        <v>2.2142134996563201E-2</v>
+      </c>
+      <c r="AQ72">
+        <v>2.2142134996563201E-2</v>
+      </c>
+      <c r="AR72">
+        <v>0.92328223139862475</v>
+      </c>
+      <c r="AS72">
+        <v>0.52645700673408502</v>
+      </c>
+      <c r="AT72">
+        <v>-0.82406108658749222</v>
+      </c>
+      <c r="AU72">
+        <v>0.2</v>
+      </c>
+      <c r="AV72" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD72">
+        <v>2.2142134996563201E-2</v>
+      </c>
+      <c r="BE72">
+        <v>0.92328223139862475</v>
+      </c>
+      <c r="BF72">
+        <v>2.2142134996563201E-2</v>
+      </c>
+      <c r="BG72">
+        <v>2.2142134996563201E-2</v>
+      </c>
+      <c r="BH72">
+        <v>0.92328223139862475</v>
+      </c>
+      <c r="BI72">
+        <v>0.52645700673408502</v>
+      </c>
+      <c r="BJ72">
+        <v>-0.82406108658749222</v>
+      </c>
+    </row>
+    <row r="73" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>250</v>
+      </c>
+      <c r="B73" t="s">
+        <v>251</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73" t="s">
+        <v>97</v>
+      </c>
+      <c r="E73" t="s">
+        <v>79</v>
+      </c>
+      <c r="F73">
+        <v>16590</v>
+      </c>
+      <c r="G73">
+        <v>4.5</v>
+      </c>
+      <c r="H73" t="s">
+        <v>206</v>
+      </c>
+      <c r="I73" t="s">
+        <v>81</v>
+      </c>
+      <c r="J73">
+        <v>5</v>
+      </c>
+      <c r="K73">
+        <v>5</v>
+      </c>
+      <c r="L73" t="s">
+        <v>82</v>
+      </c>
+      <c r="M73" t="b">
+        <v>1</v>
+      </c>
+      <c r="N73" t="b">
+        <v>0</v>
+      </c>
+      <c r="O73" t="b">
+        <v>0</v>
+      </c>
+      <c r="P73" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>249</v>
+      </c>
+      <c r="R73">
+        <v>1</v>
+      </c>
+      <c r="S73" t="s">
+        <v>85</v>
+      </c>
+      <c r="T73" t="s">
+        <v>86</v>
+      </c>
+      <c r="U73" t="s">
+        <v>87</v>
+      </c>
+      <c r="V73">
+        <v>5</v>
+      </c>
+      <c r="W73" t="s">
+        <v>208</v>
+      </c>
+      <c r="X73" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z73">
+        <v>4000</v>
+      </c>
+      <c r="AA73">
+        <v>4000</v>
+      </c>
+      <c r="AC73">
+        <v>256</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE73">
+        <v>0.15</v>
+      </c>
+      <c r="AF73" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG73">
+        <v>80</v>
+      </c>
+      <c r="AH73">
+        <v>50</v>
+      </c>
+      <c r="AI73">
+        <v>30</v>
+      </c>
+      <c r="AJ73">
+        <v>6.3959920420626704E-2</v>
+      </c>
+      <c r="AK73">
+        <v>1.60418770966844E-2</v>
+      </c>
+      <c r="AL73">
+        <v>0.94672435728000337</v>
+      </c>
+      <c r="AM73">
+        <v>7.9023756648857399E-2</v>
+      </c>
+      <c r="AN73">
+        <v>2.00969064263532E-2</v>
+      </c>
+      <c r="AO73">
+        <v>0.93036851157037204</v>
+      </c>
+      <c r="AP73">
+        <v>2.00969064263532E-2</v>
+      </c>
+      <c r="AQ73">
+        <v>2.00969064263532E-2</v>
+      </c>
+      <c r="AR73">
+        <v>0.93036851157037204</v>
+      </c>
+      <c r="AS73">
+        <v>0.26951661149108092</v>
+      </c>
+      <c r="AT73">
+        <v>6.6182505083238197E-2</v>
+      </c>
+      <c r="AU73">
+        <v>0.2</v>
+      </c>
+      <c r="AV73" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD73">
+        <v>2.00969064263532E-2</v>
+      </c>
+      <c r="BE73">
+        <v>0.93036851157037204</v>
+      </c>
+      <c r="BF73">
+        <v>2.00969064263532E-2</v>
+      </c>
+      <c r="BG73">
+        <v>2.00969064263532E-2</v>
+      </c>
+      <c r="BH73">
+        <v>0.93036851157037204</v>
+      </c>
+      <c r="BI73">
+        <v>0.26951661149108092</v>
+      </c>
+      <c r="BJ73">
+        <v>6.6182505083238197E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>252</v>
+      </c>
+      <c r="B74" t="s">
+        <v>253</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+      <c r="D74" t="s">
+        <v>78</v>
+      </c>
+      <c r="E74" t="s">
+        <v>79</v>
+      </c>
+      <c r="F74">
+        <v>16590</v>
+      </c>
+      <c r="G74">
+        <v>4.5</v>
+      </c>
+      <c r="H74" t="s">
+        <v>206</v>
+      </c>
+      <c r="I74" t="s">
+        <v>81</v>
+      </c>
+      <c r="J74">
+        <v>5</v>
+      </c>
+      <c r="K74">
+        <v>5</v>
+      </c>
+      <c r="L74" t="s">
+        <v>82</v>
+      </c>
+      <c r="M74" t="b">
+        <v>1</v>
+      </c>
+      <c r="N74" t="b">
+        <v>0</v>
+      </c>
+      <c r="O74" t="b">
+        <v>0</v>
+      </c>
+      <c r="P74" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>249</v>
+      </c>
+      <c r="R74">
+        <v>1</v>
+      </c>
+      <c r="S74" t="s">
+        <v>85</v>
+      </c>
+      <c r="T74" t="s">
+        <v>86</v>
+      </c>
+      <c r="U74" t="s">
+        <v>87</v>
+      </c>
+      <c r="V74">
+        <v>5</v>
+      </c>
+      <c r="W74" t="s">
+        <v>208</v>
+      </c>
+      <c r="X74" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z74">
+        <v>4000</v>
+      </c>
+      <c r="AA74">
+        <v>4000</v>
+      </c>
+      <c r="AC74">
+        <v>256</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE74">
+        <v>0.15</v>
+      </c>
+      <c r="AF74" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG74">
+        <v>80</v>
+      </c>
+      <c r="AH74">
+        <v>50</v>
+      </c>
+      <c r="AI74">
+        <v>30</v>
+      </c>
+      <c r="AJ74">
+        <v>7.2858124563777105E-2</v>
+      </c>
+      <c r="AK74">
+        <v>1.94210431927213E-2</v>
+      </c>
+      <c r="AL74">
+        <v>0.93550202684205275</v>
+      </c>
+      <c r="AM74">
+        <v>-0.13615874955120219</v>
+      </c>
+      <c r="AN74">
+        <v>2.2856676408924099E-2</v>
+      </c>
+      <c r="AO74">
+        <v>0.9208064980179862</v>
+      </c>
+      <c r="AP74">
+        <v>2.2856676408924099E-2</v>
+      </c>
+      <c r="AQ74">
+        <v>2.2856676408924099E-2</v>
+      </c>
+      <c r="AR74">
+        <v>0.9208064980179862</v>
+      </c>
+      <c r="AS74">
+        <v>0.34117426624687452</v>
+      </c>
+      <c r="AT74">
+        <v>-0.1820959638595927</v>
+      </c>
+      <c r="AU74">
+        <v>0.2</v>
+      </c>
+      <c r="AV74" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD74">
+        <v>2.2856676408924099E-2</v>
+      </c>
+      <c r="BE74">
+        <v>0.9208064980179862</v>
+      </c>
+      <c r="BF74">
+        <v>2.2856676408924099E-2</v>
+      </c>
+      <c r="BG74">
+        <v>2.2856676408924099E-2</v>
+      </c>
+      <c r="BH74">
+        <v>0.9208064980179862</v>
+      </c>
+      <c r="BI74">
+        <v>0.34117426624687452</v>
+      </c>
+      <c r="BJ74">
+        <v>-0.1820959638595927</v>
+      </c>
+    </row>
+    <row r="75" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>254</v>
+      </c>
+      <c r="B75" t="s">
+        <v>255</v>
+      </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
+      <c r="D75" t="s">
+        <v>97</v>
+      </c>
+      <c r="E75" t="s">
+        <v>79</v>
+      </c>
+      <c r="F75">
+        <v>16590</v>
+      </c>
+      <c r="G75">
+        <v>4.5</v>
+      </c>
+      <c r="H75" t="s">
+        <v>206</v>
+      </c>
+      <c r="I75" t="s">
+        <v>81</v>
+      </c>
+      <c r="J75">
+        <v>5</v>
+      </c>
+      <c r="K75">
+        <v>5</v>
+      </c>
+      <c r="L75" t="s">
+        <v>82</v>
+      </c>
+      <c r="M75" t="b">
+        <v>1</v>
+      </c>
+      <c r="N75" t="b">
+        <v>0</v>
+      </c>
+      <c r="O75" t="b">
+        <v>0</v>
+      </c>
+      <c r="P75" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>249</v>
+      </c>
+      <c r="R75">
+        <v>1</v>
+      </c>
+      <c r="S75" t="s">
+        <v>85</v>
+      </c>
+      <c r="T75" t="s">
+        <v>86</v>
+      </c>
+      <c r="U75" t="s">
+        <v>87</v>
+      </c>
+      <c r="V75">
+        <v>5</v>
+      </c>
+      <c r="W75" t="s">
+        <v>208</v>
+      </c>
+      <c r="X75" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z75">
+        <v>4000</v>
+      </c>
+      <c r="AA75">
+        <v>4000</v>
+      </c>
+      <c r="AC75">
+        <v>256</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE75">
+        <v>0.15</v>
+      </c>
+      <c r="AF75" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG75">
+        <v>80</v>
+      </c>
+      <c r="AH75">
+        <v>50</v>
+      </c>
+      <c r="AI75">
+        <v>30</v>
+      </c>
+      <c r="AJ75">
+        <v>7.1830306514445802E-2</v>
+      </c>
+      <c r="AK75">
+        <v>1.6258466605144E-2</v>
+      </c>
+      <c r="AL75">
+        <v>0.9460050558416464</v>
+      </c>
+      <c r="AM75">
+        <v>-0.50160609397747824</v>
+      </c>
+      <c r="AN75">
+        <v>1.7667974160849201E-2</v>
+      </c>
+      <c r="AO75">
+        <v>0.9387842430941058</v>
+      </c>
+      <c r="AP75">
+        <v>1.7667974160849201E-2</v>
+      </c>
+      <c r="AQ75">
+        <v>1.7667974160849201E-2</v>
+      </c>
+      <c r="AR75">
+        <v>0.9387842430941058</v>
+      </c>
+      <c r="AS75">
+        <v>0.42842198710792379</v>
+      </c>
+      <c r="AT75">
+        <v>-0.48439068209946679</v>
+      </c>
+      <c r="AU75">
+        <v>0.2</v>
+      </c>
+      <c r="AV75" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD75">
+        <v>1.7667974160849201E-2</v>
+      </c>
+      <c r="BE75">
+        <v>0.9387842430941058</v>
+      </c>
+      <c r="BF75">
+        <v>1.7667974160849201E-2</v>
+      </c>
+      <c r="BG75">
+        <v>1.7667974160849201E-2</v>
+      </c>
+      <c r="BH75">
+        <v>0.9387842430941058</v>
+      </c>
+      <c r="BI75">
+        <v>0.42842198710792379</v>
+      </c>
+      <c r="BJ75">
+        <v>-0.48439068209946679</v>
+      </c>
+    </row>
+    <row r="76" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>256</v>
+      </c>
+      <c r="B76" t="s">
+        <v>257</v>
+      </c>
+      <c r="C76">
+        <v>4</v>
+      </c>
+      <c r="D76" t="s">
+        <v>97</v>
+      </c>
+      <c r="E76" t="s">
+        <v>79</v>
+      </c>
+      <c r="F76">
+        <v>16590</v>
+      </c>
+      <c r="G76">
+        <v>4.5</v>
+      </c>
+      <c r="H76" t="s">
+        <v>206</v>
+      </c>
+      <c r="I76" t="s">
+        <v>81</v>
+      </c>
+      <c r="J76">
+        <v>5</v>
+      </c>
+      <c r="K76">
+        <v>5</v>
+      </c>
+      <c r="L76" t="s">
+        <v>82</v>
+      </c>
+      <c r="M76" t="b">
+        <v>1</v>
+      </c>
+      <c r="N76" t="b">
+        <v>0</v>
+      </c>
+      <c r="O76" t="b">
+        <v>0</v>
+      </c>
+      <c r="P76" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>249</v>
+      </c>
+      <c r="R76">
+        <v>1</v>
+      </c>
+      <c r="S76" t="s">
+        <v>85</v>
+      </c>
+      <c r="T76" t="s">
+        <v>86</v>
+      </c>
+      <c r="U76" t="s">
+        <v>87</v>
+      </c>
+      <c r="V76">
+        <v>5</v>
+      </c>
+      <c r="W76" t="s">
+        <v>208</v>
+      </c>
+      <c r="X76" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z76">
+        <v>4000</v>
+      </c>
+      <c r="AA76">
+        <v>4000</v>
+      </c>
+      <c r="AC76">
+        <v>256</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE76">
+        <v>0.15</v>
+      </c>
+      <c r="AF76" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG76">
+        <v>80</v>
+      </c>
+      <c r="AH76">
+        <v>50</v>
+      </c>
+      <c r="AI76">
+        <v>30</v>
+      </c>
+      <c r="AJ76">
+        <v>5.8240539245228699E-2</v>
+      </c>
+      <c r="AK76">
+        <v>1.52665596587167E-2</v>
+      </c>
+      <c r="AL76">
+        <v>0.94929921398603623</v>
+      </c>
+      <c r="AM76">
+        <v>-0.46106698875157609</v>
+      </c>
+      <c r="AN76">
+        <v>1.8232040616981901E-2</v>
+      </c>
+      <c r="AO76">
+        <v>0.93682987329805401</v>
+      </c>
+      <c r="AP76">
+        <v>1.8232040616981901E-2</v>
+      </c>
+      <c r="AQ76">
+        <v>1.8232040616981901E-2</v>
+      </c>
+      <c r="AR76">
+        <v>0.93682987329805401</v>
+      </c>
+      <c r="AS76">
+        <v>0.43637245060924618</v>
+      </c>
+      <c r="AT76">
+        <v>-0.51193734005556735</v>
+      </c>
+      <c r="AU76">
+        <v>0.2</v>
+      </c>
+      <c r="AV76" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD76">
+        <v>1.8232040616981901E-2</v>
+      </c>
+      <c r="BE76">
+        <v>0.93682987329805401</v>
+      </c>
+      <c r="BF76">
+        <v>1.8232040616981901E-2</v>
+      </c>
+      <c r="BG76">
+        <v>1.8232040616981901E-2</v>
+      </c>
+      <c r="BH76">
+        <v>0.93682987329805401</v>
+      </c>
+      <c r="BI76">
+        <v>0.43637245060924618</v>
+      </c>
+      <c r="BJ76">
+        <v>-0.51193734005556735</v>
+      </c>
+    </row>
+    <row r="77" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>258</v>
+      </c>
+      <c r="B77" t="s">
+        <v>259</v>
+      </c>
+      <c r="C77">
+        <v>5</v>
+      </c>
+      <c r="D77" t="s">
+        <v>78</v>
+      </c>
+      <c r="E77" t="s">
+        <v>79</v>
+      </c>
+      <c r="F77">
+        <v>16590</v>
+      </c>
+      <c r="G77">
+        <v>4.5</v>
+      </c>
+      <c r="H77" t="s">
+        <v>206</v>
+      </c>
+      <c r="I77" t="s">
+        <v>81</v>
+      </c>
+      <c r="J77">
+        <v>5</v>
+      </c>
+      <c r="K77">
+        <v>5</v>
+      </c>
+      <c r="L77" t="s">
+        <v>82</v>
+      </c>
+      <c r="M77" t="b">
+        <v>1</v>
+      </c>
+      <c r="N77" t="b">
+        <v>0</v>
+      </c>
+      <c r="O77" t="b">
+        <v>0</v>
+      </c>
+      <c r="P77" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>249</v>
+      </c>
+      <c r="R77">
+        <v>1</v>
+      </c>
+      <c r="S77" t="s">
+        <v>85</v>
+      </c>
+      <c r="T77" t="s">
+        <v>86</v>
+      </c>
+      <c r="U77" t="s">
+        <v>87</v>
+      </c>
+      <c r="V77">
+        <v>5</v>
+      </c>
+      <c r="W77" t="s">
+        <v>208</v>
+      </c>
+      <c r="X77" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z77">
+        <v>4000</v>
+      </c>
+      <c r="AA77">
+        <v>4000</v>
+      </c>
+      <c r="AC77">
+        <v>256</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE77">
+        <v>0.15</v>
+      </c>
+      <c r="AF77" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG77">
+        <v>80</v>
+      </c>
+      <c r="AH77">
+        <v>50</v>
+      </c>
+      <c r="AI77">
+        <v>30</v>
+      </c>
+      <c r="AJ77">
+        <v>8.0777425155601296E-2</v>
+      </c>
+      <c r="AK77">
+        <v>1.9021958250905201E-2</v>
+      </c>
+      <c r="AL77">
+        <v>0.936827402086295</v>
+      </c>
+      <c r="AM77">
+        <v>-0.50926086149150063</v>
+      </c>
+      <c r="AN77">
+        <v>2.3588723244885298E-2</v>
+      </c>
+      <c r="AO77">
+        <v>0.91827011208341558</v>
+      </c>
+      <c r="AP77">
+        <v>2.3588723244885298E-2</v>
+      </c>
+      <c r="AQ77">
+        <v>2.3588723244885298E-2</v>
+      </c>
+      <c r="AR77">
+        <v>0.91827011208341558</v>
+      </c>
+      <c r="AS77">
+        <v>0.47022945696878887</v>
+      </c>
+      <c r="AT77">
+        <v>-0.6292446358438839</v>
+      </c>
+      <c r="AU77">
+        <v>0.2</v>
+      </c>
+      <c r="AV77" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD77">
+        <v>2.3588723244885298E-2</v>
+      </c>
+      <c r="BE77">
+        <v>0.91827011208341558</v>
+      </c>
+      <c r="BF77">
+        <v>2.3588723244885298E-2</v>
+      </c>
+      <c r="BG77">
+        <v>2.3588723244885298E-2</v>
+      </c>
+      <c r="BH77">
+        <v>0.91827011208341558</v>
+      </c>
+      <c r="BI77">
+        <v>0.47022945696878887</v>
+      </c>
+      <c r="BJ77">
+        <v>-0.6292446358438839</v>
+      </c>
+    </row>
+    <row r="78" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>260</v>
+      </c>
+      <c r="B78" t="s">
+        <v>261</v>
+      </c>
+      <c r="C78">
+        <v>6</v>
+      </c>
+      <c r="D78" t="s">
+        <v>78</v>
+      </c>
+      <c r="E78" t="s">
+        <v>79</v>
+      </c>
+      <c r="F78">
+        <v>16590</v>
+      </c>
+      <c r="G78">
+        <v>4.5</v>
+      </c>
+      <c r="H78" t="s">
+        <v>206</v>
+      </c>
+      <c r="I78" t="s">
+        <v>81</v>
+      </c>
+      <c r="J78">
+        <v>5</v>
+      </c>
+      <c r="K78">
+        <v>5</v>
+      </c>
+      <c r="L78" t="s">
+        <v>82</v>
+      </c>
+      <c r="M78" t="b">
+        <v>1</v>
+      </c>
+      <c r="N78" t="b">
+        <v>0</v>
+      </c>
+      <c r="O78" t="b">
+        <v>0</v>
+      </c>
+      <c r="P78" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>249</v>
+      </c>
+      <c r="R78">
+        <v>1</v>
+      </c>
+      <c r="S78" t="s">
+        <v>85</v>
+      </c>
+      <c r="T78" t="s">
+        <v>86</v>
+      </c>
+      <c r="U78" t="s">
+        <v>87</v>
+      </c>
+      <c r="V78">
+        <v>5</v>
+      </c>
+      <c r="W78" t="s">
+        <v>208</v>
+      </c>
+      <c r="X78" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z78">
+        <v>4000</v>
+      </c>
+      <c r="AA78">
+        <v>4000</v>
+      </c>
+      <c r="AC78">
+        <v>256</v>
+      </c>
+      <c r="AD78" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE78">
+        <v>0.15</v>
+      </c>
+      <c r="AF78" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG78">
+        <v>80</v>
+      </c>
+      <c r="AH78">
+        <v>50</v>
+      </c>
+      <c r="AI78">
+        <v>30</v>
+      </c>
+      <c r="AJ78">
+        <v>5.9151062765839001E-2</v>
+      </c>
+      <c r="AK78">
+        <v>1.8484608016264299E-2</v>
+      </c>
+      <c r="AL78">
+        <v>0.93861196127121438</v>
+      </c>
+      <c r="AM78">
+        <v>-3.3766767427696603E-2</v>
+      </c>
+      <c r="AN78">
+        <v>2.0393658854090901E-2</v>
+      </c>
+      <c r="AO78">
+        <v>0.92934032778924125</v>
+      </c>
+      <c r="AP78">
+        <v>2.0393658854090901E-2</v>
+      </c>
+      <c r="AQ78">
+        <v>2.0393658854090901E-2</v>
+      </c>
+      <c r="AR78">
+        <v>0.92934032778924125</v>
+      </c>
+      <c r="AS78">
+        <v>0.29705222317799629</v>
+      </c>
+      <c r="AT78">
+        <v>-2.9222508300610101E-2</v>
+      </c>
+      <c r="AU78">
+        <v>0.2</v>
+      </c>
+      <c r="AV78" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD78">
+        <v>2.0393658854090901E-2</v>
+      </c>
+      <c r="BE78">
+        <v>0.92934032778924125</v>
+      </c>
+      <c r="BF78">
+        <v>2.0393658854090901E-2</v>
+      </c>
+      <c r="BG78">
+        <v>2.0393658854090901E-2</v>
+      </c>
+      <c r="BH78">
+        <v>0.92934032778924125</v>
+      </c>
+      <c r="BI78">
+        <v>0.29705222317799629</v>
+      </c>
+      <c r="BJ78">
+        <v>-2.9222508300610101E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>262</v>
+      </c>
+      <c r="B79" t="s">
+        <v>263</v>
+      </c>
+      <c r="C79">
+        <v>7</v>
+      </c>
+      <c r="D79" t="s">
+        <v>78</v>
+      </c>
+      <c r="E79" t="s">
+        <v>79</v>
+      </c>
+      <c r="F79">
+        <v>16590</v>
+      </c>
+      <c r="G79">
+        <v>4.5</v>
+      </c>
+      <c r="H79" t="s">
+        <v>206</v>
+      </c>
+      <c r="I79" t="s">
+        <v>81</v>
+      </c>
+      <c r="J79">
+        <v>5</v>
+      </c>
+      <c r="K79">
+        <v>5</v>
+      </c>
+      <c r="L79" t="s">
+        <v>82</v>
+      </c>
+      <c r="M79" t="b">
+        <v>1</v>
+      </c>
+      <c r="N79" t="b">
+        <v>0</v>
+      </c>
+      <c r="O79" t="b">
+        <v>0</v>
+      </c>
+      <c r="P79" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>249</v>
+      </c>
+      <c r="R79">
+        <v>1</v>
+      </c>
+      <c r="S79" t="s">
+        <v>85</v>
+      </c>
+      <c r="T79" t="s">
+        <v>86</v>
+      </c>
+      <c r="U79" t="s">
+        <v>87</v>
+      </c>
+      <c r="V79">
+        <v>5</v>
+      </c>
+      <c r="W79" t="s">
+        <v>208</v>
+      </c>
+      <c r="X79" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z79">
+        <v>4000</v>
+      </c>
+      <c r="AA79">
+        <v>4000</v>
+      </c>
+      <c r="AC79">
+        <v>256</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE79">
+        <v>0.15</v>
+      </c>
+      <c r="AF79" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG79">
+        <v>80</v>
+      </c>
+      <c r="AH79">
+        <v>50</v>
+      </c>
+      <c r="AI79">
+        <v>30</v>
+      </c>
+      <c r="AJ79">
+        <v>5.4188874681042103E-2</v>
+      </c>
+      <c r="AK79">
+        <v>1.35308519441628E-2</v>
+      </c>
+      <c r="AL79">
+        <v>0.95506356085826238</v>
+      </c>
+      <c r="AM79">
+        <v>0.1885492978150263</v>
+      </c>
+      <c r="AN79">
+        <v>1.72155310404415E-2</v>
+      </c>
+      <c r="AO79">
+        <v>0.94035186187260722</v>
+      </c>
+      <c r="AP79">
+        <v>1.72155310404415E-2</v>
+      </c>
+      <c r="AQ79">
+        <v>1.72155310404415E-2</v>
+      </c>
+      <c r="AR79">
+        <v>0.94035186187260722</v>
+      </c>
+      <c r="AS79">
+        <v>0.25060475085835782</v>
+      </c>
+      <c r="AT79">
+        <v>0.13170806294240109</v>
+      </c>
+      <c r="AU79">
+        <v>0.2</v>
+      </c>
+      <c r="AV79" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD79">
+        <v>1.72155310404415E-2</v>
+      </c>
+      <c r="BE79">
+        <v>0.94035186187260722</v>
+      </c>
+      <c r="BF79">
+        <v>1.72155310404415E-2</v>
+      </c>
+      <c r="BG79">
+        <v>1.72155310404415E-2</v>
+      </c>
+      <c r="BH79">
+        <v>0.94035186187260722</v>
+      </c>
+      <c r="BI79">
+        <v>0.25060475085835782</v>
+      </c>
+      <c r="BJ79">
+        <v>0.13170806294240109</v>
+      </c>
+    </row>
+    <row r="80" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>264</v>
+      </c>
+      <c r="B80" t="s">
+        <v>265</v>
+      </c>
+      <c r="C80">
+        <v>8</v>
+      </c>
+      <c r="D80" t="s">
+        <v>97</v>
+      </c>
+      <c r="E80" t="s">
+        <v>79</v>
+      </c>
+      <c r="F80">
+        <v>16590</v>
+      </c>
+      <c r="G80">
+        <v>4.5</v>
+      </c>
+      <c r="H80" t="s">
+        <v>206</v>
+      </c>
+      <c r="I80" t="s">
+        <v>81</v>
+      </c>
+      <c r="J80">
+        <v>5</v>
+      </c>
+      <c r="K80">
+        <v>5</v>
+      </c>
+      <c r="L80" t="s">
+        <v>82</v>
+      </c>
+      <c r="M80" t="b">
+        <v>1</v>
+      </c>
+      <c r="N80" t="b">
+        <v>0</v>
+      </c>
+      <c r="O80" t="b">
+        <v>0</v>
+      </c>
+      <c r="P80" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>249</v>
+      </c>
+      <c r="R80">
+        <v>1</v>
+      </c>
+      <c r="S80" t="s">
+        <v>85</v>
+      </c>
+      <c r="T80" t="s">
+        <v>86</v>
+      </c>
+      <c r="U80" t="s">
+        <v>87</v>
+      </c>
+      <c r="V80">
+        <v>5</v>
+      </c>
+      <c r="W80" t="s">
+        <v>208</v>
+      </c>
+      <c r="X80" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z80">
+        <v>4000</v>
+      </c>
+      <c r="AA80">
+        <v>4000</v>
+      </c>
+      <c r="AC80">
+        <v>256</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE80">
+        <v>0.15</v>
+      </c>
+      <c r="AF80" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG80">
+        <v>80</v>
+      </c>
+      <c r="AH80">
+        <v>50</v>
+      </c>
+      <c r="AI80">
+        <v>30</v>
+      </c>
+      <c r="AJ80">
+        <v>6.7964925006429602E-2</v>
+      </c>
+      <c r="AK80">
+        <v>1.8756596596358501E-2</v>
+      </c>
+      <c r="AL80">
+        <v>0.93770867755137999</v>
+      </c>
+      <c r="AM80">
+        <v>-0.23741663021914869</v>
+      </c>
+      <c r="AN80">
+        <v>2.4160365616291E-2</v>
+      </c>
+      <c r="AO80">
+        <v>0.91628949335902243</v>
+      </c>
+      <c r="AP80">
+        <v>2.4160365616291E-2</v>
+      </c>
+      <c r="AQ80">
+        <v>2.4160365616291E-2</v>
+      </c>
+      <c r="AR80">
+        <v>0.91628949335902243</v>
+      </c>
+      <c r="AS80">
+        <v>0.35232038875783661</v>
+      </c>
+      <c r="AT80">
+        <v>-0.22071489774881781</v>
+      </c>
+      <c r="AU80">
+        <v>0.2</v>
+      </c>
+      <c r="AV80" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD80">
+        <v>2.4160365616291E-2</v>
+      </c>
+      <c r="BE80">
+        <v>0.91628949335902243</v>
+      </c>
+      <c r="BF80">
+        <v>2.4160365616291E-2</v>
+      </c>
+      <c r="BG80">
+        <v>2.4160365616291E-2</v>
+      </c>
+      <c r="BH80">
+        <v>0.91628949335902243</v>
+      </c>
+      <c r="BI80">
+        <v>0.35232038875783661</v>
+      </c>
+      <c r="BJ80">
+        <v>-0.22071489774881781</v>
+      </c>
+    </row>
+    <row r="81" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>266</v>
+      </c>
+      <c r="B81" t="s">
+        <v>267</v>
+      </c>
+      <c r="C81">
+        <v>9</v>
+      </c>
+      <c r="D81" t="s">
+        <v>78</v>
+      </c>
+      <c r="E81" t="s">
+        <v>79</v>
+      </c>
+      <c r="F81">
+        <v>16590</v>
+      </c>
+      <c r="G81">
+        <v>4.5</v>
+      </c>
+      <c r="H81" t="s">
+        <v>206</v>
+      </c>
+      <c r="I81" t="s">
+        <v>81</v>
+      </c>
+      <c r="J81">
+        <v>5</v>
+      </c>
+      <c r="K81">
+        <v>5</v>
+      </c>
+      <c r="L81" t="s">
+        <v>82</v>
+      </c>
+      <c r="M81" t="b">
+        <v>1</v>
+      </c>
+      <c r="N81" t="b">
+        <v>0</v>
+      </c>
+      <c r="O81" t="b">
+        <v>0</v>
+      </c>
+      <c r="P81" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>249</v>
+      </c>
+      <c r="R81">
+        <v>1</v>
+      </c>
+      <c r="S81" t="s">
+        <v>85</v>
+      </c>
+      <c r="T81" t="s">
+        <v>86</v>
+      </c>
+      <c r="U81" t="s">
+        <v>87</v>
+      </c>
+      <c r="V81">
+        <v>5</v>
+      </c>
+      <c r="W81" t="s">
+        <v>208</v>
+      </c>
+      <c r="X81" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z81">
+        <v>4000</v>
+      </c>
+      <c r="AA81">
+        <v>4000</v>
+      </c>
+      <c r="AC81">
+        <v>256</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE81">
+        <v>0.15</v>
+      </c>
+      <c r="AF81" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG81">
+        <v>80</v>
+      </c>
+      <c r="AH81">
+        <v>50</v>
+      </c>
+      <c r="AI81">
+        <v>30</v>
+      </c>
+      <c r="AJ81">
+        <v>6.56548478243969E-2</v>
+      </c>
+      <c r="AK81">
+        <v>1.53856241943085E-2</v>
+      </c>
+      <c r="AL81">
+        <v>0.94890379644103318</v>
+      </c>
+      <c r="AM81">
+        <v>5.2215333591930299E-2</v>
+      </c>
+      <c r="AN81">
+        <v>1.8991631709616999E-2</v>
+      </c>
+      <c r="AO81">
+        <v>0.93419805239706644</v>
+      </c>
+      <c r="AP81">
+        <v>1.8991631709616999E-2</v>
+      </c>
+      <c r="AQ81">
+        <v>1.8991631709616999E-2</v>
+      </c>
+      <c r="AR81">
+        <v>0.93419805239706644</v>
+      </c>
+      <c r="AS81">
+        <v>0.23447876511905949</v>
+      </c>
+      <c r="AT81">
+        <v>0.1875811593086093</v>
+      </c>
+      <c r="AU81">
+        <v>0.2</v>
+      </c>
+      <c r="AV81" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD81">
+        <v>1.8991631709616999E-2</v>
+      </c>
+      <c r="BE81">
+        <v>0.93419805239706644</v>
+      </c>
+      <c r="BF81">
+        <v>1.8991631709616999E-2</v>
+      </c>
+      <c r="BG81">
+        <v>1.8991631709616999E-2</v>
+      </c>
+      <c r="BH81">
+        <v>0.93419805239706644</v>
+      </c>
+      <c r="BI81">
+        <v>0.23447876511905949</v>
+      </c>
+      <c r="BJ81">
+        <v>0.1875811593086093</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -13964,111 +21595,187 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90CB9F0A-C44C-4ADD-AB59-25BAE93917D6}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="3">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" t="s">
         <v>202</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C3" t="s">
         <v>203</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D3" t="s">
         <v>201</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H3" t="s">
+        <v>203</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B4" s="4">
         <v>0.96649763846131376</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C4" s="4">
         <v>0.84346352467469698</v>
-      </c>
-      <c r="D2" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.61350696560796847</v>
-      </c>
-      <c r="C3" s="4">
-        <v>-2.3261117245769642E-2</v>
-      </c>
-      <c r="D3" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.94700043924153421</v>
-      </c>
-      <c r="C4" s="4">
-        <v>-3.2540614410540742</v>
       </c>
       <c r="D4" s="4">
         <v>10</v>
       </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.96652284277514655</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.83926040542681801</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="B5" s="4">
-        <v>0.92830560542251406</v>
+        <v>0.61350696560796847</v>
       </c>
       <c r="C5" s="4">
-        <v>-0.41973551004090365</v>
+        <v>-2.3261117245769642E-2</v>
       </c>
       <c r="D5" s="4">
         <v>10</v>
       </c>
+      <c r="F5" s="3">
+        <v>3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.94139741432407242</v>
+      </c>
+      <c r="H5" s="4">
+        <v>-0.64501208493547735</v>
+      </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="B6" s="4">
-        <v>0.6149127599265698</v>
+        <v>0.94700043924153421</v>
       </c>
       <c r="C6" s="4">
-        <v>-1.8128869465603659E-2</v>
+        <v>-3.2540614410540742</v>
       </c>
       <c r="D6" s="4">
         <v>10</v>
       </c>
+      <c r="F6" s="3">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.92885212048804955</v>
+      </c>
+      <c r="H6" s="4">
+        <v>-0.24961953871611825</v>
+      </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.92830560542251406</v>
+      </c>
+      <c r="C7" s="4">
+        <v>-0.41973551004090365</v>
+      </c>
+      <c r="D7" s="4">
+        <v>10</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B7" s="4">
-        <v>0.81404468173197997</v>
-      </c>
-      <c r="C7" s="4">
-        <v>-0.57434468262633065</v>
-      </c>
-      <c r="D7" s="4">
-        <v>50</v>
+      <c r="G7" s="4">
+        <v>0.94559079252908929</v>
+      </c>
+      <c r="H7" s="4">
+        <v>-1.8457072741592515E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.6149127599265698</v>
+      </c>
+      <c r="C8" s="4">
+        <v>-1.8128869465603659E-2</v>
+      </c>
+      <c r="D8" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.96652284277514655</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.83926040542681812</v>
+      </c>
+      <c r="D9" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B10" s="4">
+        <v>0.83945770857250746</v>
+      </c>
+      <c r="C10" s="4">
+        <v>-0.33874383461747259</v>
+      </c>
+      <c r="D10" s="4">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
